--- a/mining_estimating_manual/RMM-CIVIL-CANADA-2026-MANUAL-REV1.xlsx
+++ b/mining_estimating_manual/RMM-CIVIL-CANADA-2026-MANUAL-REV1.xlsx
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3621" uniqueCount="1929">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3630" uniqueCount="1938">
   <si>
     <t>RICK MILLER SME STANDARD — CANADA 2026 MINING HEAVY CIVIL ESTIMATING MANUAL &amp; RATE LIBRARY</t>
   </si>
@@ -2878,6 +2878,9 @@
     <t>Crew cost per unit ($) [calculated]</t>
   </si>
   <si>
+    <t>= Unit MH / Prod × Crew $/hr</t>
+  </si>
+  <si>
     <t>Unit material cost ($)</t>
   </si>
   <si>
@@ -2893,6 +2896,9 @@
     <t>Adjusted material cost ($) [calc]</t>
   </si>
   <si>
+    <t>= Mat × (1+wastage)</t>
+  </si>
+  <si>
     <t>Unit subcontract cost ($)</t>
   </si>
   <si>
@@ -2908,6 +2914,9 @@
     <t>Subtotal direct + CDI ($) [calc]</t>
   </si>
   <si>
+    <t>= (Crew+Mat+Sub) × (1+CDI)</t>
+  </si>
+  <si>
     <t>Design growth (Class 3 baseline) %</t>
   </si>
   <si>
@@ -2923,6 +2932,9 @@
     <t>FINAL UNIT RATE BEFORE MARKUP STACK ($) [calc]</t>
   </si>
   <si>
+    <t>= Subtotal × (1+DG) × Regional adjustor</t>
+  </si>
+  <si>
     <t>[TEMPLATE] This calculator builds a single direct unit rate. The 6-layer markup stack (OH, Bond/Ins, Contingency, Profit) is applied at project roll-up (Sheet 21). For Sheet 08 entries already include CDI in the LOW/HIGH columns. For subcontract-dominant work (e.g. blasting, liner) set Unit MH=0 and place sub quote in Subcontract row.</t>
   </si>
   <si>
@@ -5209,6 +5221,9 @@
     <t>CDI AMOUNT</t>
   </si>
   <si>
+    <t>= Direct × CDI %</t>
+  </si>
+  <si>
     <t>3.1</t>
   </si>
   <si>
@@ -5221,6 +5236,9 @@
     <t>COMPANY OH AMOUNT</t>
   </si>
   <si>
+    <t>= Direct × OH %</t>
+  </si>
+  <si>
     <t>4.1</t>
   </si>
   <si>
@@ -5233,6 +5251,9 @@
     <t>BOND + INSURANCE AMOUNT</t>
   </si>
   <si>
+    <t>= (Direct + CDI + OH) × B+I %</t>
+  </si>
+  <si>
     <t>5.1</t>
   </si>
   <si>
@@ -5245,6 +5266,9 @@
     <t>CONTINGENCY AMOUNT</t>
   </si>
   <si>
+    <t>= Direct × Contingency %</t>
+  </si>
+  <si>
     <t>6.1</t>
   </si>
   <si>
@@ -5252,6 +5276,9 @@
   </si>
   <si>
     <t>PROFIT AMOUNT</t>
+  </si>
+  <si>
+    <t>= (Direct + CDI + OH + B+I + Cont.) × Profit %</t>
   </si>
   <si>
     <t>TOTAL BID (CAD)</t>
@@ -6759,119 +6786,115 @@
         <f>B10/B11*B9</f>
         <v>0</v>
       </c>
-      <c r="C12" s="4">
-        <f> Unit MH / Prod × Crew $/hr</f>
-        <v>0</v>
+      <c r="C12" s="4" t="s">
+        <v>945</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="22" customHeight="1">
       <c r="A13" s="4" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="B13" s="16">
         <v>0</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="22" customHeight="1">
       <c r="A14" s="4" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="B14" s="16">
         <v>0.05</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="22" customHeight="1">
       <c r="A15" s="3" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="B15" s="17">
         <f>B13*(1+B14)</f>
         <v>0</v>
       </c>
-      <c r="C15" s="4">
-        <f> Mat × (1+wastage)</f>
-        <v>0</v>
+      <c r="C15" s="4" t="s">
+        <v>951</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="22" customHeight="1">
       <c r="A16" s="4" t="s">
-        <v>950</v>
+        <v>952</v>
       </c>
       <c r="B16" s="16">
         <v>0</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>951</v>
+        <v>953</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="22" customHeight="1">
       <c r="A17" s="4" t="s">
-        <v>952</v>
+        <v>954</v>
       </c>
       <c r="B17" s="16">
         <v>0.06</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>953</v>
+        <v>955</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="22" customHeight="1">
       <c r="A18" s="3" t="s">
-        <v>954</v>
+        <v>956</v>
       </c>
       <c r="B18" s="17">
         <f>(B12+B15+B16)*(1+B17)</f>
         <v>0</v>
       </c>
-      <c r="C18" s="4">
-        <f> (Crew+Mat+Sub) × (1+CDI)</f>
-        <v>0</v>
+      <c r="C18" s="4" t="s">
+        <v>957</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="22" customHeight="1">
       <c r="A19" s="4" t="s">
-        <v>955</v>
+        <v>958</v>
       </c>
       <c r="B19" s="16">
         <v>0.1</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>956</v>
+        <v>959</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="22" customHeight="1">
       <c r="A20" s="4" t="s">
-        <v>957</v>
+        <v>960</v>
       </c>
       <c r="B20" s="16">
         <v>1</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>958</v>
+        <v>961</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="26" customHeight="1">
       <c r="A21" s="3" t="s">
-        <v>959</v>
+        <v>962</v>
       </c>
       <c r="B21" s="17">
         <f>B18*(1+B19)*B20</f>
         <v>0</v>
       </c>
-      <c r="C21" s="4">
-        <f> Subtotal × (1+DG) × Regional adjustor</f>
-        <v>0</v>
+      <c r="C21" s="4" t="s">
+        <v>963</v>
       </c>
     </row>
     <row r="23" spans="1:8">
       <c r="A23" s="13" t="s">
-        <v>960</v>
+        <v>964</v>
       </c>
       <c r="B23" s="13"/>
       <c r="C23" s="13"/>
@@ -6926,7 +6949,7 @@
     </row>
     <row r="3" spans="1:6" ht="22" customHeight="1">
       <c r="A3" s="5" t="s">
-        <v>961</v>
+        <v>965</v>
       </c>
       <c r="B3" s="5"/>
       <c r="C3" s="5"/>
@@ -6936,33 +6959,33 @@
     </row>
     <row r="4" spans="1:6" ht="32" customHeight="1">
       <c r="A4" s="6" t="s">
-        <v>962</v>
+        <v>966</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>963</v>
+        <v>967</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>596</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>964</v>
+        <v>968</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>965</v>
+        <v>969</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>966</v>
+        <v>970</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="24" customHeight="1">
       <c r="A5" s="3" t="s">
-        <v>967</v>
+        <v>971</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>968</v>
+        <v>972</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>969</v>
+        <v>973</v>
       </c>
       <c r="D5" s="11">
         <v>55</v>
@@ -6971,18 +6994,18 @@
         <v>120</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>970</v>
+        <v>974</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="24" customHeight="1">
       <c r="A6" s="3" t="s">
-        <v>967</v>
+        <v>971</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>971</v>
+        <v>975</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>969</v>
+        <v>973</v>
       </c>
       <c r="D6" s="11">
         <v>22</v>
@@ -6991,18 +7014,18 @@
         <v>45</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>972</v>
+        <v>976</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="24" customHeight="1">
       <c r="A7" s="3" t="s">
-        <v>967</v>
+        <v>971</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>973</v>
+        <v>977</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>974</v>
+        <v>978</v>
       </c>
       <c r="D7" s="11">
         <v>22</v>
@@ -7011,18 +7034,18 @@
         <v>42</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>975</v>
+        <v>979</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="24" customHeight="1">
       <c r="A8" s="3" t="s">
-        <v>967</v>
+        <v>971</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>976</v>
+        <v>980</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>974</v>
+        <v>978</v>
       </c>
       <c r="D8" s="11">
         <v>65</v>
@@ -7036,13 +7059,13 @@
     </row>
     <row r="9" spans="1:6" ht="24" customHeight="1">
       <c r="A9" s="3" t="s">
-        <v>967</v>
+        <v>971</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>977</v>
+        <v>981</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>978</v>
+        <v>982</v>
       </c>
       <c r="D9" s="11">
         <v>8500</v>
@@ -7051,18 +7074,18 @@
         <v>18000</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>979</v>
+        <v>983</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="24" customHeight="1">
       <c r="A10" s="3" t="s">
-        <v>980</v>
+        <v>984</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>981</v>
+        <v>985</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>969</v>
+        <v>973</v>
       </c>
       <c r="D10" s="11">
         <v>22</v>
@@ -7071,18 +7094,18 @@
         <v>45</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>982</v>
+        <v>986</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="24" customHeight="1">
       <c r="A11" s="3" t="s">
-        <v>980</v>
+        <v>984</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>983</v>
+        <v>987</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>974</v>
+        <v>978</v>
       </c>
       <c r="D11" s="11">
         <v>28</v>
@@ -7091,18 +7114,18 @@
         <v>55</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>984</v>
+        <v>988</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="24" customHeight="1">
       <c r="A12" s="3" t="s">
-        <v>980</v>
+        <v>984</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>985</v>
+        <v>989</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>986</v>
+        <v>990</v>
       </c>
       <c r="D12" s="11">
         <v>280</v>
@@ -7111,18 +7134,18 @@
         <v>500</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>987</v>
+        <v>991</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="24" customHeight="1">
       <c r="A13" s="3" t="s">
-        <v>988</v>
+        <v>992</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>989</v>
+        <v>993</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>986</v>
+        <v>990</v>
       </c>
       <c r="D13" s="11">
         <v>1000</v>
@@ -7134,13 +7157,13 @@
     </row>
     <row r="14" spans="1:6" ht="24" customHeight="1">
       <c r="A14" s="3" t="s">
-        <v>988</v>
+        <v>992</v>
       </c>
       <c r="B14" s="4" t="s">
+        <v>994</v>
+      </c>
+      <c r="C14" s="7" t="s">
         <v>990</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>986</v>
       </c>
       <c r="D14" s="11">
         <v>230</v>
@@ -7149,18 +7172,18 @@
         <v>380</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>991</v>
+        <v>995</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="24" customHeight="1">
       <c r="A15" s="3" t="s">
-        <v>988</v>
+        <v>992</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>992</v>
+        <v>996</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>993</v>
+        <v>997</v>
       </c>
       <c r="D15" s="11">
         <v>2200</v>
@@ -7172,13 +7195,13 @@
     </row>
     <row r="16" spans="1:6" ht="24" customHeight="1">
       <c r="A16" s="3" t="s">
-        <v>988</v>
+        <v>992</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>994</v>
+        <v>998</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>993</v>
+        <v>997</v>
       </c>
       <c r="D16" s="11">
         <v>8000</v>
@@ -7190,13 +7213,13 @@
     </row>
     <row r="17" spans="1:6" ht="24" customHeight="1">
       <c r="A17" s="3" t="s">
-        <v>995</v>
+        <v>999</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>996</v>
+        <v>1000</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>969</v>
+        <v>973</v>
       </c>
       <c r="D17" s="11">
         <v>2200</v>
@@ -7205,18 +7228,18 @@
         <v>3500</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>997</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="24" customHeight="1">
       <c r="A18" s="3" t="s">
-        <v>995</v>
+        <v>999</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>998</v>
+        <v>1002</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>974</v>
+        <v>978</v>
       </c>
       <c r="D18" s="11">
         <v>90</v>
@@ -7225,18 +7248,18 @@
         <v>160</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>999</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="24" customHeight="1">
       <c r="A19" s="3" t="s">
-        <v>995</v>
+        <v>999</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>1000</v>
+        <v>1004</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>1001</v>
+        <v>1005</v>
       </c>
       <c r="D19" s="11">
         <v>3800</v>
@@ -7245,18 +7268,18 @@
         <v>6500</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>1002</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="24" customHeight="1">
       <c r="A20" s="3" t="s">
-        <v>1003</v>
+        <v>1007</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>1004</v>
+        <v>1008</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>1005</v>
+        <v>1009</v>
       </c>
       <c r="D20" s="11">
         <v>3000</v>
@@ -7265,18 +7288,18 @@
         <v>9000</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>1006</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="24" customHeight="1">
       <c r="A21" s="3" t="s">
-        <v>1007</v>
+        <v>1011</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>1008</v>
+        <v>1012</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>986</v>
+        <v>990</v>
       </c>
       <c r="D21" s="11">
         <v>150</v>
@@ -7285,18 +7308,18 @@
         <v>280</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>1009</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="24" customHeight="1">
       <c r="A22" s="3" t="s">
-        <v>1010</v>
+        <v>1014</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>1011</v>
+        <v>1015</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>993</v>
+        <v>997</v>
       </c>
       <c r="D22" s="11">
         <v>4000</v>
@@ -7310,42 +7333,42 @@
     </row>
     <row r="23" spans="1:6" ht="24" customHeight="1">
       <c r="A23" s="3" t="s">
-        <v>1012</v>
+        <v>1016</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>1013</v>
+        <v>1017</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>1014</v>
+        <v>1018</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>1015</v>
+        <v>1019</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>1016</v>
+        <v>1020</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>1017</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="24" customHeight="1">
       <c r="A24" s="3" t="s">
-        <v>1012</v>
+        <v>1016</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>1018</v>
+        <v>1022</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>1019</v>
+        <v>1023</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>1020</v>
+        <v>1024</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>1021</v>
+        <v>1025</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>1022</v>
+        <v>1026</v>
       </c>
     </row>
   </sheetData>
@@ -7392,7 +7415,7 @@
     </row>
     <row r="3" spans="1:6" ht="22" customHeight="1">
       <c r="A3" s="5" t="s">
-        <v>1023</v>
+        <v>1027</v>
       </c>
       <c r="B3" s="5"/>
       <c r="C3" s="5"/>
@@ -7402,7 +7425,7 @@
     </row>
     <row r="4" spans="1:6" ht="32" customHeight="1">
       <c r="A4" s="6" t="s">
-        <v>962</v>
+        <v>966</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>223</v>
@@ -7411,10 +7434,10 @@
         <v>596</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>1024</v>
+        <v>1028</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>1025</v>
+        <v>1029</v>
       </c>
       <c r="F4" s="6" t="s">
         <v>301</v>
@@ -7422,7 +7445,7 @@
     </row>
     <row r="5" spans="1:6" ht="18" customHeight="1">
       <c r="A5" s="9" t="s">
-        <v>1026</v>
+        <v>1030</v>
       </c>
       <c r="B5" s="9"/>
       <c r="C5" s="9"/>
@@ -7432,13 +7455,13 @@
     </row>
     <row r="6" spans="1:6" ht="24" customHeight="1">
       <c r="A6" s="4" t="s">
-        <v>1026</v>
+        <v>1030</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>1027</v>
+        <v>1031</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>1028</v>
+        <v>1032</v>
       </c>
       <c r="D6" s="11">
         <v>1500</v>
@@ -7450,13 +7473,13 @@
     </row>
     <row r="7" spans="1:6" ht="24" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>1026</v>
+        <v>1030</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>1029</v>
+        <v>1033</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>1028</v>
+        <v>1032</v>
       </c>
       <c r="D7" s="11">
         <v>4500</v>
@@ -7465,18 +7488,18 @@
         <v>8500</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>1030</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="24" customHeight="1">
       <c r="A8" s="4" t="s">
-        <v>1026</v>
+        <v>1030</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>1031</v>
+        <v>1035</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>1028</v>
+        <v>1032</v>
       </c>
       <c r="D8" s="11">
         <v>9500</v>
@@ -7488,13 +7511,13 @@
     </row>
     <row r="9" spans="1:6" ht="24" customHeight="1">
       <c r="A9" s="4" t="s">
-        <v>1026</v>
+        <v>1030</v>
       </c>
       <c r="B9" s="4" t="s">
+        <v>1036</v>
+      </c>
+      <c r="C9" s="7" t="s">
         <v>1032</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>1028</v>
       </c>
       <c r="D9" s="11">
         <v>850</v>
@@ -7503,18 +7526,18 @@
         <v>2500</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>1033</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="24" customHeight="1">
       <c r="A10" s="4" t="s">
-        <v>1026</v>
+        <v>1030</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>1034</v>
+        <v>1038</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>1028</v>
+        <v>1032</v>
       </c>
       <c r="D10" s="11">
         <v>1200</v>
@@ -7523,18 +7546,18 @@
         <v>1800</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>1035</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="24" customHeight="1">
       <c r="A11" s="4" t="s">
-        <v>1026</v>
+        <v>1030</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>1036</v>
+        <v>1040</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>1028</v>
+        <v>1032</v>
       </c>
       <c r="D11" s="11">
         <v>3500</v>
@@ -7543,15 +7566,15 @@
         <v>6500</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>1037</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="24" customHeight="1">
       <c r="A12" s="4" t="s">
-        <v>1026</v>
+        <v>1030</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C12" s="7" t="s">
         <v>842</v>
@@ -7563,12 +7586,12 @@
         <v>85000</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>1039</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="18" customHeight="1">
       <c r="A13" s="9" t="s">
-        <v>1040</v>
+        <v>1044</v>
       </c>
       <c r="B13" s="9"/>
       <c r="C13" s="9"/>
@@ -7578,13 +7601,13 @@
     </row>
     <row r="14" spans="1:6" ht="24" customHeight="1">
       <c r="A14" s="4" t="s">
-        <v>1040</v>
+        <v>1044</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>1041</v>
+        <v>1045</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>1028</v>
+        <v>1032</v>
       </c>
       <c r="D14" s="11">
         <v>14000</v>
@@ -7596,13 +7619,13 @@
     </row>
     <row r="15" spans="1:6" ht="24" customHeight="1">
       <c r="A15" s="4" t="s">
-        <v>1040</v>
+        <v>1044</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>1042</v>
+        <v>1046</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>1028</v>
+        <v>1032</v>
       </c>
       <c r="D15" s="11">
         <v>11000</v>
@@ -7614,13 +7637,13 @@
     </row>
     <row r="16" spans="1:6" ht="24" customHeight="1">
       <c r="A16" s="4" t="s">
-        <v>1040</v>
+        <v>1044</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>1043</v>
+        <v>1047</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>1028</v>
+        <v>1032</v>
       </c>
       <c r="D16" s="11">
         <v>12000</v>
@@ -7629,18 +7652,18 @@
         <v>17000</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>1044</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="24" customHeight="1">
       <c r="A17" s="4" t="s">
-        <v>1040</v>
+        <v>1044</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>1045</v>
+        <v>1049</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>1028</v>
+        <v>1032</v>
       </c>
       <c r="D17" s="11">
         <v>16000</v>
@@ -7652,13 +7675,13 @@
     </row>
     <row r="18" spans="1:6" ht="24" customHeight="1">
       <c r="A18" s="4" t="s">
-        <v>1040</v>
+        <v>1044</v>
       </c>
       <c r="B18" s="4" t="s">
         <v>310</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>1028</v>
+        <v>1032</v>
       </c>
       <c r="D18" s="11">
         <v>13000</v>
@@ -7670,13 +7693,13 @@
     </row>
     <row r="19" spans="1:6" ht="24" customHeight="1">
       <c r="A19" s="4" t="s">
-        <v>1040</v>
+        <v>1044</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>1046</v>
+        <v>1050</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>1028</v>
+        <v>1032</v>
       </c>
       <c r="D19" s="11">
         <v>7500</v>
@@ -7688,7 +7711,7 @@
     </row>
     <row r="20" spans="1:6" ht="18" customHeight="1">
       <c r="A20" s="9" t="s">
-        <v>1047</v>
+        <v>1051</v>
       </c>
       <c r="B20" s="9"/>
       <c r="C20" s="9"/>
@@ -7698,13 +7721,13 @@
     </row>
     <row r="21" spans="1:6" ht="24" customHeight="1">
       <c r="A21" s="4" t="s">
-        <v>1047</v>
+        <v>1051</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>1048</v>
+        <v>1052</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>1049</v>
+        <v>1053</v>
       </c>
       <c r="D21" s="11">
         <v>850</v>
@@ -7713,18 +7736,18 @@
         <v>1500</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>1050</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="24" customHeight="1">
       <c r="A22" s="4" t="s">
-        <v>1047</v>
+        <v>1051</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>1051</v>
+        <v>1055</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>1052</v>
+        <v>1056</v>
       </c>
       <c r="D22" s="11">
         <v>185</v>
@@ -7733,18 +7756,18 @@
         <v>350</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>1053</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="24" customHeight="1">
       <c r="A23" s="4" t="s">
-        <v>1047</v>
+        <v>1051</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>1054</v>
+        <v>1058</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>1055</v>
+        <v>1059</v>
       </c>
       <c r="D23" s="11">
         <v>250</v>
@@ -7753,18 +7776,18 @@
         <v>450</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>1056</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="24" customHeight="1">
       <c r="A24" s="4" t="s">
-        <v>1047</v>
+        <v>1051</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>1057</v>
+        <v>1061</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>1058</v>
+        <v>1062</v>
       </c>
       <c r="D24" s="11">
         <v>2.5</v>
@@ -7773,18 +7796,18 @@
         <v>4.5</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>1059</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="24" customHeight="1">
       <c r="A25" s="4" t="s">
-        <v>1047</v>
+        <v>1051</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>1060</v>
+        <v>1064</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>1049</v>
+        <v>1053</v>
       </c>
       <c r="D25" s="11">
         <v>2500</v>
@@ -7793,12 +7816,12 @@
         <v>4500</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>1061</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="18" customHeight="1">
       <c r="A26" s="9" t="s">
-        <v>1062</v>
+        <v>1066</v>
       </c>
       <c r="B26" s="9"/>
       <c r="C26" s="9"/>
@@ -7808,13 +7831,13 @@
     </row>
     <row r="27" spans="1:6" ht="24" customHeight="1">
       <c r="A27" s="4" t="s">
-        <v>1062</v>
+        <v>1066</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>1063</v>
+        <v>1067</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>1028</v>
+        <v>1032</v>
       </c>
       <c r="D27" s="11">
         <v>350</v>
@@ -7823,18 +7846,18 @@
         <v>750</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>1064</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="24" customHeight="1">
       <c r="A28" s="4" t="s">
-        <v>1062</v>
+        <v>1066</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>1065</v>
+        <v>1069</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>1066</v>
+        <v>1070</v>
       </c>
       <c r="D28" s="11">
         <v>450</v>
@@ -7843,18 +7866,18 @@
         <v>950</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>1067</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="24" customHeight="1">
       <c r="A29" s="4" t="s">
-        <v>1062</v>
+        <v>1066</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>1068</v>
+        <v>1072</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>1028</v>
+        <v>1032</v>
       </c>
       <c r="D29" s="11">
         <v>5500</v>
@@ -7863,12 +7886,12 @@
         <v>9500</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>1069</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="18" customHeight="1">
       <c r="A30" s="9" t="s">
-        <v>1070</v>
+        <v>1074</v>
       </c>
       <c r="B30" s="9"/>
       <c r="C30" s="9"/>
@@ -7878,27 +7901,27 @@
     </row>
     <row r="31" spans="1:6" ht="24" customHeight="1">
       <c r="A31" s="4" t="s">
-        <v>1070</v>
+        <v>1074</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>1071</v>
+        <v>1075</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>1019</v>
+        <v>1023</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>1072</v>
+        <v>1076</v>
       </c>
       <c r="E31" s="7" t="s">
-        <v>1073</v>
+        <v>1077</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>1074</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="33" spans="1:6">
       <c r="A33" s="13" t="s">
-        <v>1075</v>
+        <v>1079</v>
       </c>
       <c r="B33" s="13"/>
       <c r="C33" s="13"/>
@@ -7956,7 +7979,7 @@
     </row>
     <row r="3" spans="1:6" ht="22" customHeight="1">
       <c r="A3" s="5" t="s">
-        <v>1076</v>
+        <v>1080</v>
       </c>
       <c r="B3" s="5"/>
       <c r="C3" s="5"/>
@@ -7966,7 +7989,7 @@
     </row>
     <row r="4" spans="1:6" ht="32" customHeight="1">
       <c r="A4" s="6" t="s">
-        <v>962</v>
+        <v>966</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>223</v>
@@ -7975,10 +7998,10 @@
         <v>207</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>1077</v>
+        <v>1081</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>1078</v>
+        <v>1082</v>
       </c>
       <c r="F4" s="6" t="s">
         <v>301</v>
@@ -7986,7 +8009,7 @@
     </row>
     <row r="5" spans="1:6" ht="18" customHeight="1">
       <c r="A5" s="9" t="s">
-        <v>1079</v>
+        <v>1083</v>
       </c>
       <c r="B5" s="9"/>
       <c r="C5" s="9"/>
@@ -7996,127 +8019,127 @@
     </row>
     <row r="6" spans="1:6" ht="24" customHeight="1">
       <c r="A6" s="4" t="s">
-        <v>1079</v>
+        <v>1083</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>1080</v>
+        <v>1084</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>1081</v>
+        <v>1085</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>1082</v>
+        <v>1086</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>1083</v>
+        <v>1087</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>1084</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="24" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>1079</v>
+        <v>1083</v>
       </c>
       <c r="B7" s="4" t="s">
+        <v>1089</v>
+      </c>
+      <c r="C7" s="4" t="s">
         <v>1085</v>
       </c>
-      <c r="C7" s="4" t="s">
-        <v>1081</v>
-      </c>
       <c r="D7" s="7" t="s">
-        <v>1073</v>
+        <v>1077</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>1086</v>
+        <v>1090</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>1087</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="24" customHeight="1">
       <c r="A8" s="4" t="s">
-        <v>1079</v>
+        <v>1083</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>1088</v>
+        <v>1092</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>1081</v>
+        <v>1085</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>1020</v>
+        <v>1024</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>1021</v>
+        <v>1025</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>1089</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="24" customHeight="1">
       <c r="A9" s="4" t="s">
-        <v>1079</v>
+        <v>1083</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>1090</v>
+        <v>1094</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>1081</v>
+        <v>1085</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>1072</v>
+        <v>1076</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>1073</v>
+        <v>1077</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>1091</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="24" customHeight="1">
       <c r="A10" s="4" t="s">
-        <v>1079</v>
+        <v>1083</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>1092</v>
+        <v>1096</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>1081</v>
+        <v>1085</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>1072</v>
+        <v>1076</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>1073</v>
+        <v>1077</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>1093</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="24" customHeight="1">
       <c r="A11" s="4" t="s">
-        <v>1079</v>
+        <v>1083</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>1094</v>
+        <v>1098</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>1095</v>
+        <v>1099</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>1096</v>
+        <v>1100</v>
       </c>
       <c r="E11" s="7" t="s">
         <v>818</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>1097</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="18" customHeight="1">
       <c r="A12" s="9" t="s">
-        <v>1098</v>
+        <v>1102</v>
       </c>
       <c r="B12" s="9"/>
       <c r="C12" s="9"/>
@@ -8126,27 +8149,27 @@
     </row>
     <row r="13" spans="1:6" ht="24" customHeight="1">
       <c r="A13" s="4" t="s">
-        <v>1098</v>
+        <v>1102</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>1099</v>
+        <v>1103</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>1100</v>
+        <v>1104</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>1101</v>
+        <v>1105</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>1102</v>
+        <v>1106</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>1103</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="18" customHeight="1">
       <c r="A14" s="9" t="s">
-        <v>1104</v>
+        <v>1108</v>
       </c>
       <c r="B14" s="9"/>
       <c r="C14" s="9"/>
@@ -8156,147 +8179,147 @@
     </row>
     <row r="15" spans="1:6" ht="24" customHeight="1">
       <c r="A15" s="4" t="s">
-        <v>1104</v>
+        <v>1108</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>1105</v>
+        <v>1109</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>1106</v>
+        <v>1110</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>1107</v>
+        <v>1111</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>1108</v>
+        <v>1112</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="24" customHeight="1">
       <c r="A16" s="4" t="s">
-        <v>1104</v>
+        <v>1108</v>
       </c>
       <c r="B16" s="4" t="s">
+        <v>1114</v>
+      </c>
+      <c r="C16" s="4" t="s">
         <v>1110</v>
       </c>
-      <c r="C16" s="4" t="s">
-        <v>1106</v>
-      </c>
       <c r="D16" s="7" t="s">
-        <v>1111</v>
+        <v>1115</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>1112</v>
+        <v>1116</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>1113</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="24" customHeight="1">
       <c r="A17" s="4" t="s">
-        <v>1104</v>
+        <v>1108</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>1114</v>
+        <v>1118</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>1106</v>
+        <v>1110</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>1107</v>
+        <v>1111</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>1115</v>
+        <v>1119</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>1116</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="24" customHeight="1">
       <c r="A18" s="4" t="s">
-        <v>1104</v>
+        <v>1108</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>1117</v>
+        <v>1121</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>1106</v>
+        <v>1110</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>1118</v>
+        <v>1122</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>1119</v>
+        <v>1123</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>1120</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="24" customHeight="1">
       <c r="A19" s="4" t="s">
-        <v>1104</v>
+        <v>1108</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>1121</v>
+        <v>1125</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>1106</v>
+        <v>1110</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>1115</v>
+        <v>1119</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>1122</v>
+        <v>1126</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>1123</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="24" customHeight="1">
       <c r="A20" s="4" t="s">
-        <v>1104</v>
+        <v>1108</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>1124</v>
+        <v>1128</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>1106</v>
+        <v>1110</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>1125</v>
+        <v>1129</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>1126</v>
+        <v>1130</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>1127</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="24" customHeight="1">
       <c r="A21" s="4" t="s">
-        <v>1104</v>
+        <v>1108</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>1128</v>
+        <v>1132</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>1106</v>
+        <v>1110</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>1115</v>
+        <v>1119</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>1122</v>
+        <v>1126</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>1129</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="18" customHeight="1">
       <c r="A22" s="9" t="s">
-        <v>1130</v>
+        <v>1134</v>
       </c>
       <c r="B22" s="9"/>
       <c r="C22" s="9"/>
@@ -8306,27 +8329,27 @@
     </row>
     <row r="23" spans="1:6" ht="24" customHeight="1">
       <c r="A23" s="4" t="s">
-        <v>1130</v>
+        <v>1134</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>1131</v>
+        <v>1135</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>1132</v>
+        <v>1136</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>1072</v>
+        <v>1076</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>1133</v>
+        <v>1137</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>1134</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="25" spans="1:6">
       <c r="A25" s="13" t="s">
-        <v>1135</v>
+        <v>1139</v>
       </c>
       <c r="B25" s="13"/>
       <c r="C25" s="13"/>
@@ -8382,7 +8405,7 @@
     </row>
     <row r="3" spans="1:6" ht="22" customHeight="1">
       <c r="A3" s="5" t="s">
-        <v>1136</v>
+        <v>1140</v>
       </c>
       <c r="B3" s="5"/>
       <c r="C3" s="5"/>
@@ -8392,7 +8415,7 @@
     </row>
     <row r="4" spans="1:6" ht="32" customHeight="1">
       <c r="A4" s="6" t="s">
-        <v>962</v>
+        <v>966</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>223</v>
@@ -8401,10 +8424,10 @@
         <v>596</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>1024</v>
+        <v>1028</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>1025</v>
+        <v>1029</v>
       </c>
       <c r="F4" s="6" t="s">
         <v>301</v>
@@ -8412,7 +8435,7 @@
     </row>
     <row r="5" spans="1:6" ht="18" customHeight="1">
       <c r="A5" s="9" t="s">
-        <v>1137</v>
+        <v>1141</v>
       </c>
       <c r="B5" s="9"/>
       <c r="C5" s="9"/>
@@ -8422,13 +8445,13 @@
     </row>
     <row r="6" spans="1:6" ht="24" customHeight="1">
       <c r="A6" s="4" t="s">
-        <v>1137</v>
+        <v>1141</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>1138</v>
+        <v>1142</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>1139</v>
+        <v>1143</v>
       </c>
       <c r="D6" s="11">
         <v>110</v>
@@ -8440,13 +8463,13 @@
     </row>
     <row r="7" spans="1:6" ht="24" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>1137</v>
+        <v>1141</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>1140</v>
+        <v>1144</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>1139</v>
+        <v>1143</v>
       </c>
       <c r="D7" s="11">
         <v>140</v>
@@ -8458,13 +8481,13 @@
     </row>
     <row r="8" spans="1:6" ht="24" customHeight="1">
       <c r="A8" s="4" t="s">
-        <v>1137</v>
+        <v>1141</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>1141</v>
+        <v>1145</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>1139</v>
+        <v>1143</v>
       </c>
       <c r="D8" s="11">
         <v>155</v>
@@ -8476,13 +8499,13 @@
     </row>
     <row r="9" spans="1:6" ht="24" customHeight="1">
       <c r="A9" s="4" t="s">
-        <v>1137</v>
+        <v>1141</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>1142</v>
+        <v>1146</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>1139</v>
+        <v>1143</v>
       </c>
       <c r="D9" s="11">
         <v>110</v>
@@ -8494,13 +8517,13 @@
     </row>
     <row r="10" spans="1:6" ht="24" customHeight="1">
       <c r="A10" s="4" t="s">
-        <v>1137</v>
+        <v>1141</v>
       </c>
       <c r="B10" s="4" t="s">
+        <v>1147</v>
+      </c>
+      <c r="C10" s="7" t="s">
         <v>1143</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>1139</v>
       </c>
       <c r="D10" s="11">
         <v>320</v>
@@ -8509,18 +8532,18 @@
         <v>480</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>1144</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="24" customHeight="1">
       <c r="A11" s="4" t="s">
-        <v>1137</v>
+        <v>1141</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>1145</v>
+        <v>1149</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>1139</v>
+        <v>1143</v>
       </c>
       <c r="D11" s="11">
         <v>850</v>
@@ -8529,12 +8552,12 @@
         <v>1300</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>1146</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="18" customHeight="1">
       <c r="A12" s="9" t="s">
-        <v>1147</v>
+        <v>1151</v>
       </c>
       <c r="B12" s="9"/>
       <c r="C12" s="9"/>
@@ -8544,13 +8567,13 @@
     </row>
     <row r="13" spans="1:6" ht="24" customHeight="1">
       <c r="A13" s="4" t="s">
-        <v>1147</v>
+        <v>1151</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>1148</v>
+        <v>1152</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>1139</v>
+        <v>1143</v>
       </c>
       <c r="D13" s="11">
         <v>93</v>
@@ -8559,18 +8582,18 @@
         <v>128</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>1149</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="24" customHeight="1">
       <c r="A14" s="4" t="s">
-        <v>1147</v>
+        <v>1151</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>1150</v>
+        <v>1154</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>1049</v>
+        <v>1053</v>
       </c>
       <c r="D14" s="11">
         <v>7000</v>
@@ -8579,12 +8602,12 @@
         <v>10000</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>1151</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="18" customHeight="1">
       <c r="A15" s="9" t="s">
-        <v>1152</v>
+        <v>1156</v>
       </c>
       <c r="B15" s="9"/>
       <c r="C15" s="9"/>
@@ -8594,33 +8617,33 @@
     </row>
     <row r="16" spans="1:6" ht="24" customHeight="1">
       <c r="A16" s="4" t="s">
-        <v>1152</v>
+        <v>1156</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>1153</v>
+        <v>1157</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>1154</v>
+        <v>1158</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>1155</v>
+        <v>1159</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>1155</v>
+        <v>1159</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>1156</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="24" customHeight="1">
       <c r="A17" s="4" t="s">
-        <v>1152</v>
+        <v>1156</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>1157</v>
+        <v>1161</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>1154</v>
+        <v>1158</v>
       </c>
       <c r="D17" s="7" t="s">
         <v>195</v>
@@ -8629,18 +8652,18 @@
         <v>193</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>1158</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="24" customHeight="1">
       <c r="A18" s="4" t="s">
-        <v>1152</v>
+        <v>1156</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>1159</v>
+        <v>1163</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>1154</v>
+        <v>1158</v>
       </c>
       <c r="D18" s="7" t="s">
         <v>193</v>
@@ -8649,18 +8672,18 @@
         <v>189</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>1158</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="24" customHeight="1">
       <c r="A19" s="4" t="s">
-        <v>1152</v>
+        <v>1156</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>1160</v>
+        <v>1164</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>1049</v>
+        <v>1053</v>
       </c>
       <c r="D19" s="11">
         <v>450</v>
@@ -8669,18 +8692,18 @@
         <v>850</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>1161</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="24" customHeight="1">
       <c r="A20" s="4" t="s">
-        <v>1152</v>
+        <v>1156</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>1162</v>
+        <v>1166</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>1163</v>
+        <v>1167</v>
       </c>
       <c r="D20" s="11">
         <v>8</v>
@@ -8689,18 +8712,18 @@
         <v>18</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>1164</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="24" customHeight="1">
       <c r="A21" s="4" t="s">
-        <v>1152</v>
+        <v>1156</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>1165</v>
+        <v>1169</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>1166</v>
+        <v>1170</v>
       </c>
       <c r="D21" s="11">
         <v>3.5</v>
@@ -8709,12 +8732,12 @@
         <v>8.5</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>1167</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="18" customHeight="1">
       <c r="A22" s="9" t="s">
-        <v>1168</v>
+        <v>1172</v>
       </c>
       <c r="B22" s="9"/>
       <c r="C22" s="9"/>
@@ -8724,13 +8747,13 @@
     </row>
     <row r="23" spans="1:6" ht="24" customHeight="1">
       <c r="A23" s="4" t="s">
-        <v>1168</v>
+        <v>1172</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>1169</v>
+        <v>1173</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>1170</v>
+        <v>1174</v>
       </c>
       <c r="D23" s="11">
         <v>15000</v>
@@ -8739,18 +8762,18 @@
         <v>65000</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>1171</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="24" customHeight="1">
       <c r="A24" s="4" t="s">
-        <v>1168</v>
+        <v>1172</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>1172</v>
+        <v>1176</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>1173</v>
+        <v>1177</v>
       </c>
       <c r="D24" s="11">
         <v>12000</v>
@@ -8759,18 +8782,18 @@
         <v>35000</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>1174</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="24" customHeight="1">
       <c r="A25" s="4" t="s">
-        <v>1168</v>
+        <v>1172</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>1175</v>
+        <v>1179</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>1176</v>
+        <v>1180</v>
       </c>
       <c r="D25" s="7" t="s">
         <v>197</v>
@@ -8779,7 +8802,7 @@
         <v>211</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>1177</v>
+        <v>1181</v>
       </c>
     </row>
   </sheetData>
@@ -8827,7 +8850,7 @@
     </row>
     <row r="3" spans="1:5" ht="22" customHeight="1">
       <c r="A3" s="5" t="s">
-        <v>1178</v>
+        <v>1182</v>
       </c>
       <c r="B3" s="5"/>
       <c r="C3" s="5"/>
@@ -8836,10 +8859,10 @@
     </row>
     <row r="4" spans="1:5" ht="32" customHeight="1">
       <c r="A4" s="6" t="s">
-        <v>962</v>
+        <v>966</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>1179</v>
+        <v>1183</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>224</v>
@@ -8848,12 +8871,12 @@
         <v>225</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>1180</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="18" customHeight="1">
       <c r="A5" s="9" t="s">
-        <v>1181</v>
+        <v>1185</v>
       </c>
       <c r="B5" s="9"/>
       <c r="C5" s="9"/>
@@ -8862,10 +8885,10 @@
     </row>
     <row r="6" spans="1:5" ht="22" customHeight="1">
       <c r="A6" s="4" t="s">
-        <v>1181</v>
+        <v>1185</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>1182</v>
+        <v>1186</v>
       </c>
       <c r="C6" s="7" t="s">
         <v>197</v>
@@ -8874,49 +8897,49 @@
         <v>195</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>1183</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="22" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>1181</v>
+        <v>1185</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>1184</v>
+        <v>1188</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>1185</v>
+        <v>1189</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>1186</v>
+        <v>1190</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>1187</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="22" customHeight="1">
       <c r="A8" s="4" t="s">
-        <v>1181</v>
+        <v>1185</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>1188</v>
+        <v>1192</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>1189</v>
+        <v>1193</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>1190</v>
+        <v>1194</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>1191</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="22" customHeight="1">
       <c r="A9" s="4" t="s">
-        <v>1181</v>
+        <v>1185</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>1192</v>
+        <v>1196</v>
       </c>
       <c r="C9" s="7" t="s">
         <v>211</v>
@@ -8925,32 +8948,32 @@
         <v>212</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>1193</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="22" customHeight="1">
       <c r="A10" s="4" t="s">
-        <v>1181</v>
+        <v>1185</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>1194</v>
+        <v>1198</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>1083</v>
+        <v>1087</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>1195</v>
+        <v>1199</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>1196</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="22" customHeight="1">
       <c r="A11" s="4" t="s">
-        <v>1181</v>
+        <v>1185</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>1197</v>
+        <v>1201</v>
       </c>
       <c r="C11" s="7" t="s">
         <v>211</v>
@@ -8959,29 +8982,29 @@
         <v>212</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>1198</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="22" customHeight="1">
       <c r="A12" s="4" t="s">
-        <v>1181</v>
+        <v>1185</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>1199</v>
+        <v>1203</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>1200</v>
+        <v>1204</v>
       </c>
       <c r="D12" s="7" t="s">
         <v>193</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>1201</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="18" customHeight="1">
       <c r="A13" s="9" t="s">
-        <v>1202</v>
+        <v>1206</v>
       </c>
       <c r="B13" s="9"/>
       <c r="C13" s="9"/>
@@ -8990,10 +9013,10 @@
     </row>
     <row r="14" spans="1:5" ht="22" customHeight="1">
       <c r="A14" s="4" t="s">
-        <v>1202</v>
+        <v>1206</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>1203</v>
+        <v>1207</v>
       </c>
       <c r="C14" s="7" t="s">
         <v>189</v>
@@ -9002,15 +9025,15 @@
         <v>190</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>1204</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="22" customHeight="1">
       <c r="A15" s="4" t="s">
-        <v>1202</v>
+        <v>1206</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>1205</v>
+        <v>1209</v>
       </c>
       <c r="C15" s="7" t="s">
         <v>193</v>
@@ -9019,15 +9042,15 @@
         <v>189</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>1206</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="22" customHeight="1">
       <c r="A16" s="4" t="s">
-        <v>1202</v>
+        <v>1206</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>1207</v>
+        <v>1211</v>
       </c>
       <c r="C16" s="7" t="s">
         <v>195</v>
@@ -9036,15 +9059,15 @@
         <v>193</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>1208</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="22" customHeight="1">
       <c r="A17" s="4" t="s">
-        <v>1202</v>
+        <v>1206</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>1209</v>
+        <v>1213</v>
       </c>
       <c r="C17" s="7" t="s">
         <v>197</v>
@@ -9058,10 +9081,10 @@
     </row>
     <row r="18" spans="1:5" ht="22" customHeight="1">
       <c r="A18" s="4" t="s">
-        <v>1202</v>
+        <v>1206</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>1210</v>
+        <v>1214</v>
       </c>
       <c r="C18" s="7" t="s">
         <v>201</v>
@@ -9075,7 +9098,7 @@
     </row>
     <row r="19" spans="1:5" ht="18" customHeight="1">
       <c r="A19" s="9" t="s">
-        <v>1211</v>
+        <v>1215</v>
       </c>
       <c r="B19" s="9"/>
       <c r="C19" s="9"/>
@@ -9084,10 +9107,10 @@
     </row>
     <row r="20" spans="1:5" ht="22" customHeight="1">
       <c r="A20" s="4" t="s">
-        <v>1211</v>
+        <v>1215</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>1212</v>
+        <v>1216</v>
       </c>
       <c r="C20" s="7" t="s">
         <v>195</v>
@@ -9101,10 +9124,10 @@
     </row>
     <row r="21" spans="1:5" ht="22" customHeight="1">
       <c r="A21" s="4" t="s">
-        <v>1211</v>
+        <v>1215</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>1213</v>
+        <v>1217</v>
       </c>
       <c r="C21" s="7" t="s">
         <v>211</v>
@@ -9113,15 +9136,15 @@
         <v>212</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>1214</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="22" customHeight="1">
       <c r="A22" s="4" t="s">
-        <v>1211</v>
+        <v>1215</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>1215</v>
+        <v>1219</v>
       </c>
       <c r="C22" s="7" t="s">
         <v>215</v>
@@ -9130,15 +9153,15 @@
         <v>216</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>1216</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="22" customHeight="1">
       <c r="A23" s="4" t="s">
-        <v>1211</v>
+        <v>1215</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>1217</v>
+        <v>1221</v>
       </c>
       <c r="C23" s="7" t="s">
         <v>195</v>
@@ -9152,10 +9175,10 @@
     </row>
     <row r="24" spans="1:5" ht="22" customHeight="1">
       <c r="A24" s="4" t="s">
-        <v>1211</v>
+        <v>1215</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>1218</v>
+        <v>1222</v>
       </c>
       <c r="C24" s="7" t="s">
         <v>193</v>
@@ -9164,12 +9187,12 @@
         <v>189</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>1219</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="18" customHeight="1">
       <c r="A25" s="9" t="s">
-        <v>1220</v>
+        <v>1224</v>
       </c>
       <c r="B25" s="9"/>
       <c r="C25" s="9"/>
@@ -9178,180 +9201,180 @@
     </row>
     <row r="26" spans="1:5" ht="22" customHeight="1">
       <c r="A26" s="4" t="s">
-        <v>1220</v>
+        <v>1224</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>1221</v>
+        <v>1225</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>1222</v>
+        <v>1226</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>1223</v>
+        <v>1227</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>1224</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="22" customHeight="1">
       <c r="A27" s="4" t="s">
-        <v>1220</v>
+        <v>1224</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>1225</v>
+        <v>1229</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>1226</v>
+        <v>1230</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>1227</v>
+        <v>1231</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>1228</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="22" customHeight="1">
       <c r="A28" s="4" t="s">
-        <v>1220</v>
+        <v>1224</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>1229</v>
+        <v>1233</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>1230</v>
+        <v>1234</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>1231</v>
+        <v>1235</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>1232</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="22" customHeight="1">
       <c r="A29" s="4" t="s">
-        <v>1220</v>
+        <v>1224</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>1233</v>
+        <v>1237</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>1234</v>
+        <v>1238</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>1235</v>
+        <v>1239</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>1236</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="22" customHeight="1">
       <c r="A30" s="4" t="s">
-        <v>1220</v>
+        <v>1224</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>1237</v>
+        <v>1241</v>
       </c>
       <c r="C30" s="7" t="s">
+        <v>1242</v>
+      </c>
+      <c r="D30" s="7" t="s">
         <v>1238</v>
       </c>
-      <c r="D30" s="7" t="s">
-        <v>1234</v>
-      </c>
       <c r="E30" s="4" t="s">
-        <v>1239</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="22" customHeight="1">
       <c r="A31" s="4" t="s">
-        <v>1220</v>
+        <v>1224</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>1240</v>
+        <v>1244</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>1222</v>
+        <v>1226</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>1241</v>
+        <v>1245</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>1242</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="22" customHeight="1">
       <c r="A32" s="4" t="s">
-        <v>1220</v>
+        <v>1224</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>1243</v>
+        <v>1247</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>1223</v>
+        <v>1227</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>1244</v>
+        <v>1248</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>1245</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="22" customHeight="1">
       <c r="A33" s="4" t="s">
-        <v>1220</v>
+        <v>1224</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>1246</v>
+        <v>1250</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>1227</v>
+        <v>1231</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>1247</v>
+        <v>1251</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>1248</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="22" customHeight="1">
       <c r="A34" s="4" t="s">
-        <v>1220</v>
+        <v>1224</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>1249</v>
+        <v>1253</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>1223</v>
+        <v>1227</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>1250</v>
+        <v>1254</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>1251</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="22" customHeight="1">
       <c r="A35" s="4" t="s">
-        <v>1220</v>
+        <v>1224</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>1252</v>
+        <v>1256</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>1250</v>
+        <v>1254</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>1253</v>
+        <v>1257</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>1254</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="22" customHeight="1">
       <c r="A36" s="4" t="s">
-        <v>1220</v>
+        <v>1224</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>1255</v>
+        <v>1259</v>
       </c>
       <c r="C36" s="7" t="s">
         <v>193</v>
@@ -9360,12 +9383,12 @@
         <v>251</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>1256</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="18" customHeight="1">
       <c r="A37" s="9" t="s">
-        <v>1257</v>
+        <v>1261</v>
       </c>
       <c r="B37" s="9"/>
       <c r="C37" s="9"/>
@@ -9374,10 +9397,10 @@
     </row>
     <row r="38" spans="1:5" ht="22" customHeight="1">
       <c r="A38" s="4" t="s">
-        <v>1257</v>
+        <v>1261</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>1258</v>
+        <v>1262</v>
       </c>
       <c r="C38" s="7" t="s">
         <v>228</v>
@@ -9391,10 +9414,10 @@
     </row>
     <row r="39" spans="1:5" ht="22" customHeight="1">
       <c r="A39" s="4" t="s">
-        <v>1257</v>
+        <v>1261</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>1259</v>
+        <v>1263</v>
       </c>
       <c r="C39" s="7" t="s">
         <v>232</v>
@@ -9408,10 +9431,10 @@
     </row>
     <row r="40" spans="1:5" ht="22" customHeight="1">
       <c r="A40" s="4" t="s">
-        <v>1257</v>
+        <v>1261</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>1260</v>
+        <v>1264</v>
       </c>
       <c r="C40" s="7" t="s">
         <v>236</v>
@@ -9425,10 +9448,10 @@
     </row>
     <row r="41" spans="1:5" ht="22" customHeight="1">
       <c r="A41" s="4" t="s">
-        <v>1257</v>
+        <v>1261</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>1261</v>
+        <v>1265</v>
       </c>
       <c r="C41" s="7" t="s">
         <v>240</v>
@@ -9437,15 +9460,15 @@
         <v>241</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>1262</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="42" spans="1:5" ht="22" customHeight="1">
       <c r="A42" s="4" t="s">
-        <v>1257</v>
+        <v>1261</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>1263</v>
+        <v>1267</v>
       </c>
       <c r="C42" s="7" t="s">
         <v>244</v>
@@ -9454,15 +9477,15 @@
         <v>245</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>1264</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="43" spans="1:5" ht="22" customHeight="1">
       <c r="A43" s="4" t="s">
-        <v>1257</v>
+        <v>1261</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>1265</v>
+        <v>1269</v>
       </c>
       <c r="C43" s="7" t="s">
         <v>247</v>
@@ -9476,10 +9499,10 @@
     </row>
     <row r="44" spans="1:5" ht="22" customHeight="1">
       <c r="A44" s="4" t="s">
-        <v>1257</v>
+        <v>1261</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>1266</v>
+        <v>1270</v>
       </c>
       <c r="C44" s="7" t="s">
         <v>251</v>
@@ -9488,15 +9511,15 @@
         <v>251</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>1267</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="45" spans="1:5" ht="22" customHeight="1">
       <c r="A45" s="4" t="s">
-        <v>1257</v>
+        <v>1261</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>1268</v>
+        <v>1272</v>
       </c>
       <c r="C45" s="7" t="s">
         <v>251</v>
@@ -9505,12 +9528,12 @@
         <v>251</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>1269</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="46" spans="1:5" ht="18" customHeight="1">
       <c r="A46" s="9" t="s">
-        <v>1270</v>
+        <v>1274</v>
       </c>
       <c r="B46" s="9"/>
       <c r="C46" s="9"/>
@@ -9519,10 +9542,10 @@
     </row>
     <row r="47" spans="1:5" ht="22" customHeight="1">
       <c r="A47" s="4" t="s">
-        <v>1270</v>
+        <v>1274</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>1271</v>
+        <v>1275</v>
       </c>
       <c r="C47" s="7" t="s">
         <v>157</v>
@@ -9531,15 +9554,15 @@
         <v>158</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>1272</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="48" spans="1:5" ht="22" customHeight="1">
       <c r="A48" s="4" t="s">
-        <v>1270</v>
+        <v>1274</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>1273</v>
+        <v>1277</v>
       </c>
       <c r="C48" s="7" t="s">
         <v>164</v>
@@ -9548,15 +9571,15 @@
         <v>165</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>1274</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="49" spans="1:5" ht="22" customHeight="1">
       <c r="A49" s="4" t="s">
-        <v>1270</v>
+        <v>1274</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>1275</v>
+        <v>1279</v>
       </c>
       <c r="C49" s="7" t="s">
         <v>171</v>
@@ -9565,15 +9588,15 @@
         <v>172</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>1276</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="50" spans="1:5" ht="22" customHeight="1">
       <c r="A50" s="4" t="s">
-        <v>1270</v>
+        <v>1274</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>1277</v>
+        <v>1281</v>
       </c>
       <c r="C50" s="7" t="s">
         <v>178</v>
@@ -9638,7 +9661,7 @@
     </row>
     <row r="3" spans="1:7" ht="22" customHeight="1">
       <c r="A3" s="5" t="s">
-        <v>1278</v>
+        <v>1282</v>
       </c>
       <c r="B3" s="5"/>
       <c r="C3" s="5"/>
@@ -9649,22 +9672,22 @@
     </row>
     <row r="4" spans="1:7" ht="32" customHeight="1">
       <c r="A4" s="6" t="s">
-        <v>1279</v>
+        <v>1283</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>1280</v>
+        <v>1284</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>1281</v>
+        <v>1285</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>1282</v>
+        <v>1286</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>1283</v>
+        <v>1287</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>1284</v>
+        <v>1288</v>
       </c>
       <c r="G4" s="6" t="s">
         <v>301</v>
@@ -9672,7 +9695,7 @@
     </row>
     <row r="5" spans="1:7" ht="20" customHeight="1">
       <c r="A5" s="5" t="s">
-        <v>1285</v>
+        <v>1289</v>
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="5"/>
@@ -9683,13 +9706,13 @@
     </row>
     <row r="6" spans="1:7" ht="26" customHeight="1">
       <c r="A6" s="4" t="s">
-        <v>1285</v>
+        <v>1289</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>1286</v>
+        <v>1290</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>1287</v>
+        <v>1291</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>818</v>
@@ -9698,19 +9721,19 @@
         <v>818</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>1288</v>
+        <v>1292</v>
       </c>
       <c r="G6" s="4"/>
     </row>
     <row r="7" spans="1:7" ht="26" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>1285</v>
+        <v>1289</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>1289</v>
+        <v>1293</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>1287</v>
+        <v>1291</v>
       </c>
       <c r="D7" s="7" t="s">
         <v>818</v>
@@ -9719,19 +9742,19 @@
         <v>818</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>1290</v>
+        <v>1294</v>
       </c>
       <c r="G7" s="4"/>
     </row>
     <row r="8" spans="1:7" ht="26" customHeight="1">
       <c r="A8" s="4" t="s">
-        <v>1285</v>
+        <v>1289</v>
       </c>
       <c r="B8" s="4" t="s">
+        <v>1295</v>
+      </c>
+      <c r="C8" s="4" t="s">
         <v>1291</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>1287</v>
       </c>
       <c r="D8" s="7" t="s">
         <v>818</v>
@@ -9740,21 +9763,21 @@
         <v>818</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>1292</v>
+        <v>1296</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>1293</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="26" customHeight="1">
       <c r="A9" s="4" t="s">
-        <v>1285</v>
+        <v>1289</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>1294</v>
+        <v>1298</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>1287</v>
+        <v>1291</v>
       </c>
       <c r="D9" s="7" t="s">
         <v>818</v>
@@ -9763,21 +9786,21 @@
         <v>818</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>1288</v>
+        <v>1292</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>1295</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="26" customHeight="1">
       <c r="A10" s="4" t="s">
-        <v>1285</v>
+        <v>1289</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>1296</v>
+        <v>1300</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>1287</v>
+        <v>1291</v>
       </c>
       <c r="D10" s="7" t="s">
         <v>818</v>
@@ -9786,19 +9809,19 @@
         <v>818</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>1297</v>
+        <v>1301</v>
       </c>
       <c r="G10" s="4"/>
     </row>
     <row r="11" spans="1:7" ht="26" customHeight="1">
       <c r="A11" s="4" t="s">
-        <v>1285</v>
+        <v>1289</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>1298</v>
+        <v>1302</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>1287</v>
+        <v>1291</v>
       </c>
       <c r="D11" s="7" t="s">
         <v>818</v>
@@ -9807,21 +9830,21 @@
         <v>818</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>1299</v>
+        <v>1303</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>1300</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="26" customHeight="1">
       <c r="A12" s="4" t="s">
-        <v>1285</v>
+        <v>1289</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>1301</v>
+        <v>1305</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>1287</v>
+        <v>1291</v>
       </c>
       <c r="D12" s="7" t="s">
         <v>818</v>
@@ -9830,21 +9853,21 @@
         <v>818</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>1299</v>
+        <v>1303</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>1302</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="26" customHeight="1">
       <c r="A13" s="4" t="s">
-        <v>1285</v>
+        <v>1289</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>1303</v>
+        <v>1307</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>1287</v>
+        <v>1291</v>
       </c>
       <c r="D13" s="7" t="s">
         <v>818</v>
@@ -9853,21 +9876,21 @@
         <v>818</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>1304</v>
+        <v>1308</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>1305</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="26" customHeight="1">
       <c r="A14" s="4" t="s">
-        <v>1285</v>
+        <v>1289</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>1306</v>
+        <v>1310</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>1287</v>
+        <v>1291</v>
       </c>
       <c r="D14" s="7" t="s">
         <v>818</v>
@@ -9876,19 +9899,19 @@
         <v>818</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>1304</v>
+        <v>1308</v>
       </c>
       <c r="G14" s="4"/>
     </row>
     <row r="15" spans="1:7" ht="26" customHeight="1">
       <c r="A15" s="4" t="s">
-        <v>1285</v>
+        <v>1289</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>1307</v>
+        <v>1311</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>1287</v>
+        <v>1291</v>
       </c>
       <c r="D15" s="7" t="s">
         <v>818</v>
@@ -9897,21 +9920,21 @@
         <v>818</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>1308</v>
+        <v>1312</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>1309</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="26" customHeight="1">
       <c r="A16" s="4" t="s">
-        <v>1285</v>
+        <v>1289</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>1310</v>
+        <v>1314</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>1287</v>
+        <v>1291</v>
       </c>
       <c r="D16" s="7" t="s">
         <v>818</v>
@@ -9920,19 +9943,19 @@
         <v>818</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>1311</v>
+        <v>1315</v>
       </c>
       <c r="G16" s="4"/>
     </row>
     <row r="17" spans="1:7" ht="26" customHeight="1">
       <c r="A17" s="4" t="s">
-        <v>1285</v>
+        <v>1289</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>1312</v>
+        <v>1316</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>1287</v>
+        <v>1291</v>
       </c>
       <c r="D17" s="7" t="s">
         <v>818</v>
@@ -9941,21 +9964,21 @@
         <v>818</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>1304</v>
+        <v>1308</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>1313</v>
+        <v>1317</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="26" customHeight="1">
       <c r="A18" s="4" t="s">
-        <v>1285</v>
+        <v>1289</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>1314</v>
+        <v>1318</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>1315</v>
+        <v>1319</v>
       </c>
       <c r="D18" s="7" t="s">
         <v>818</v>
@@ -9964,15 +9987,15 @@
         <v>818</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>1155</v>
+        <v>1159</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>1316</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="20" customHeight="1">
       <c r="A19" s="5" t="s">
-        <v>1317</v>
+        <v>1321</v>
       </c>
       <c r="B19" s="5"/>
       <c r="C19" s="5"/>
@@ -9983,34 +10006,34 @@
     </row>
     <row r="20" spans="1:7" ht="26" customHeight="1">
       <c r="A20" s="4" t="s">
-        <v>1317</v>
+        <v>1321</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>1318</v>
+        <v>1322</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>1319</v>
+        <v>1323</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>1072</v>
+        <v>1076</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>1082</v>
+        <v>1086</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>1320</v>
+        <v>1324</v>
       </c>
       <c r="G20" s="4"/>
     </row>
     <row r="21" spans="1:7" ht="26" customHeight="1">
       <c r="A21" s="4" t="s">
-        <v>1317</v>
+        <v>1321</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>1321</v>
+        <v>1325</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>1322</v>
+        <v>1326</v>
       </c>
       <c r="D21" s="7" t="s">
         <v>211</v>
@@ -10019,109 +10042,109 @@
         <v>212</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>1323</v>
+        <v>1327</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>1324</v>
+        <v>1328</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="26" customHeight="1">
       <c r="A22" s="4" t="s">
-        <v>1317</v>
+        <v>1321</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>1325</v>
+        <v>1329</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>1326</v>
+        <v>1330</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>1083</v>
+        <v>1087</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>1327</v>
+        <v>1331</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>1328</v>
+        <v>1332</v>
       </c>
       <c r="G22" s="4"/>
     </row>
     <row r="23" spans="1:7" ht="26" customHeight="1">
       <c r="A23" s="4" t="s">
-        <v>1317</v>
+        <v>1321</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>1329</v>
+        <v>1333</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>1330</v>
+        <v>1334</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>1072</v>
+        <v>1076</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>1082</v>
+        <v>1086</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>1320</v>
+        <v>1324</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>1331</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="26" customHeight="1">
       <c r="A24" s="4" t="s">
-        <v>1317</v>
+        <v>1321</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>1332</v>
+        <v>1336</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>1333</v>
+        <v>1337</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>1334</v>
+        <v>1338</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>1335</v>
+        <v>1339</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>1336</v>
+        <v>1340</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>1337</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="26" customHeight="1">
       <c r="A25" s="4" t="s">
-        <v>1317</v>
+        <v>1321</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>1338</v>
+        <v>1342</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>1320</v>
+        <v>1324</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>1072</v>
+        <v>1076</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>1082</v>
+        <v>1086</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>1320</v>
+        <v>1324</v>
       </c>
       <c r="G25" s="4"/>
     </row>
     <row r="26" spans="1:7" ht="26" customHeight="1">
       <c r="A26" s="4" t="s">
-        <v>1317</v>
+        <v>1321</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>1339</v>
+        <v>1343</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>1340</v>
+        <v>1344</v>
       </c>
       <c r="D26" s="7" t="s">
         <v>818</v>
@@ -10130,59 +10153,59 @@
         <v>818</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>1341</v>
+        <v>1345</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>1342</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="26" customHeight="1">
       <c r="A27" s="4" t="s">
-        <v>1317</v>
+        <v>1321</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>1343</v>
+        <v>1347</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>1344</v>
+        <v>1348</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>1102</v>
+        <v>1106</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>1345</v>
+        <v>1349</v>
       </c>
       <c r="F27" s="7" t="s">
         <v>842</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>1346</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="26" customHeight="1">
       <c r="A28" s="4" t="s">
-        <v>1317</v>
+        <v>1321</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>1347</v>
+        <v>1351</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>1348</v>
+        <v>1352</v>
       </c>
       <c r="D28" s="7" t="s">
         <v>212</v>
       </c>
       <c r="E28" s="7" t="s">
-        <v>1349</v>
+        <v>1353</v>
       </c>
       <c r="F28" s="7" t="s">
-        <v>1350</v>
+        <v>1354</v>
       </c>
       <c r="G28" s="4"/>
     </row>
     <row r="29" spans="1:7" ht="20" customHeight="1">
       <c r="A29" s="5" t="s">
-        <v>1351</v>
+        <v>1355</v>
       </c>
       <c r="B29" s="5"/>
       <c r="C29" s="5"/>
@@ -10193,70 +10216,70 @@
     </row>
     <row r="30" spans="1:7" ht="26" customHeight="1">
       <c r="A30" s="4" t="s">
-        <v>1351</v>
+        <v>1355</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>1352</v>
+        <v>1356</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>1320</v>
+        <v>1324</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>1072</v>
+        <v>1076</v>
       </c>
       <c r="E30" s="7" t="s">
-        <v>1082</v>
+        <v>1086</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>1320</v>
+        <v>1324</v>
       </c>
       <c r="G30" s="4"/>
     </row>
     <row r="31" spans="1:7" ht="26" customHeight="1">
       <c r="A31" s="4" t="s">
-        <v>1351</v>
+        <v>1355</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>1353</v>
+        <v>1357</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>1354</v>
+        <v>1358</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>1072</v>
+        <v>1076</v>
       </c>
       <c r="E31" s="7" t="s">
-        <v>1073</v>
+        <v>1077</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>1355</v>
+        <v>1359</v>
       </c>
       <c r="G31" s="4"/>
     </row>
     <row r="32" spans="1:7" ht="26" customHeight="1">
       <c r="A32" s="4" t="s">
-        <v>1351</v>
+        <v>1355</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>1356</v>
+        <v>1360</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>1357</v>
+        <v>1361</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>1200</v>
+        <v>1204</v>
       </c>
       <c r="E32" s="7" t="s">
         <v>212</v>
       </c>
       <c r="F32" s="7" t="s">
-        <v>1358</v>
+        <v>1362</v>
       </c>
       <c r="G32" s="4"/>
     </row>
     <row r="33" spans="1:7" ht="20" customHeight="1">
       <c r="A33" s="5" t="s">
-        <v>1359</v>
+        <v>1363</v>
       </c>
       <c r="B33" s="5"/>
       <c r="C33" s="5"/>
@@ -10267,137 +10290,137 @@
     </row>
     <row r="34" spans="1:7" ht="26" customHeight="1">
       <c r="A34" s="4" t="s">
-        <v>1359</v>
+        <v>1363</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>1360</v>
+        <v>1364</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>1072</v>
+        <v>1076</v>
       </c>
       <c r="E34" s="7" t="s">
-        <v>1082</v>
+        <v>1086</v>
       </c>
       <c r="F34" s="7" t="s">
-        <v>1320</v>
+        <v>1324</v>
       </c>
       <c r="G34" s="4" t="s">
-        <v>1362</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="35" spans="1:7" ht="26" customHeight="1">
       <c r="A35" s="4" t="s">
+        <v>1363</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>1367</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>1358</v>
+      </c>
+      <c r="D35" s="7" t="s">
+        <v>1076</v>
+      </c>
+      <c r="E35" s="7" t="s">
+        <v>1077</v>
+      </c>
+      <c r="F35" s="7" t="s">
         <v>1359</v>
       </c>
-      <c r="B35" s="4" t="s">
-        <v>1363</v>
-      </c>
-      <c r="C35" s="4" t="s">
-        <v>1354</v>
-      </c>
-      <c r="D35" s="7" t="s">
-        <v>1072</v>
-      </c>
-      <c r="E35" s="7" t="s">
-        <v>1073</v>
-      </c>
-      <c r="F35" s="7" t="s">
-        <v>1355</v>
-      </c>
       <c r="G35" s="4" t="s">
-        <v>1364</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="36" spans="1:7" ht="26" customHeight="1">
       <c r="A36" s="4" t="s">
-        <v>1359</v>
+        <v>1363</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>1365</v>
+        <v>1369</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>1366</v>
+        <v>1370</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>1367</v>
+        <v>1371</v>
       </c>
       <c r="E36" s="7" t="s">
-        <v>1368</v>
+        <v>1372</v>
       </c>
       <c r="F36" s="7" t="s">
-        <v>1369</v>
+        <v>1373</v>
       </c>
       <c r="G36" s="4"/>
     </row>
     <row r="37" spans="1:7" ht="26" customHeight="1">
       <c r="A37" s="4" t="s">
-        <v>1359</v>
+        <v>1363</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>1370</v>
+        <v>1374</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>1371</v>
+        <v>1375</v>
       </c>
       <c r="D37" s="7" t="s">
-        <v>1111</v>
+        <v>1115</v>
       </c>
       <c r="E37" s="7" t="s">
-        <v>1112</v>
+        <v>1116</v>
       </c>
       <c r="F37" s="7" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="G37" s="4"/>
     </row>
     <row r="38" spans="1:7" ht="26" customHeight="1">
       <c r="A38" s="4" t="s">
-        <v>1359</v>
+        <v>1363</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>1373</v>
+        <v>1377</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>1374</v>
+        <v>1378</v>
       </c>
       <c r="D38" s="7" t="s">
-        <v>1375</v>
+        <v>1379</v>
       </c>
       <c r="E38" s="7" t="s">
-        <v>1376</v>
+        <v>1380</v>
       </c>
       <c r="F38" s="7" t="s">
-        <v>1377</v>
+        <v>1381</v>
       </c>
       <c r="G38" s="4"/>
     </row>
     <row r="39" spans="1:7" ht="26" customHeight="1">
       <c r="A39" s="4" t="s">
-        <v>1359</v>
+        <v>1363</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>1378</v>
+        <v>1382</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>1379</v>
+        <v>1383</v>
       </c>
       <c r="D39" s="7" t="s">
         <v>197</v>
       </c>
       <c r="E39" s="7" t="s">
-        <v>1195</v>
+        <v>1199</v>
       </c>
       <c r="F39" s="7" t="s">
-        <v>1380</v>
+        <v>1384</v>
       </c>
       <c r="G39" s="4"/>
     </row>
     <row r="40" spans="1:7" ht="20" customHeight="1">
       <c r="A40" s="5" t="s">
-        <v>1381</v>
+        <v>1385</v>
       </c>
       <c r="B40" s="5"/>
       <c r="C40" s="5"/>
@@ -10408,13 +10431,13 @@
     </row>
     <row r="41" spans="1:7" ht="26" customHeight="1">
       <c r="A41" s="4" t="s">
-        <v>1381</v>
+        <v>1385</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>1382</v>
+        <v>1386</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>1383</v>
+        <v>1387</v>
       </c>
       <c r="D41" s="7" t="s">
         <v>215</v>
@@ -10423,21 +10446,21 @@
         <v>211</v>
       </c>
       <c r="F41" s="7" t="s">
-        <v>1384</v>
+        <v>1388</v>
       </c>
       <c r="G41" s="4" t="s">
-        <v>1385</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="42" spans="1:7" ht="26" customHeight="1">
       <c r="A42" s="4" t="s">
-        <v>1381</v>
+        <v>1385</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>1386</v>
+        <v>1390</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>1387</v>
+        <v>1391</v>
       </c>
       <c r="D42" s="7" t="s">
         <v>197</v>
@@ -10446,21 +10469,21 @@
         <v>195</v>
       </c>
       <c r="F42" s="7" t="s">
-        <v>1304</v>
+        <v>1308</v>
       </c>
       <c r="G42" s="4" t="s">
-        <v>1388</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="43" spans="1:7" ht="26" customHeight="1">
       <c r="A43" s="4" t="s">
-        <v>1381</v>
+        <v>1385</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>1389</v>
+        <v>1393</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>1390</v>
+        <v>1394</v>
       </c>
       <c r="D43" s="7" t="s">
         <v>215</v>
@@ -10469,42 +10492,42 @@
         <v>211</v>
       </c>
       <c r="F43" s="7" t="s">
-        <v>1391</v>
+        <v>1395</v>
       </c>
       <c r="G43" s="4" t="s">
-        <v>1392</v>
+        <v>1396</v>
       </c>
     </row>
     <row r="44" spans="1:7" ht="26" customHeight="1">
       <c r="A44" s="4" t="s">
-        <v>1381</v>
+        <v>1385</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>1393</v>
+        <v>1397</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>1394</v>
+        <v>1398</v>
       </c>
       <c r="D44" s="7" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="E44" s="7" t="s">
         <v>215</v>
       </c>
       <c r="F44" s="7" t="s">
-        <v>1396</v>
+        <v>1400</v>
       </c>
       <c r="G44" s="4"/>
     </row>
     <row r="45" spans="1:7" ht="26" customHeight="1">
       <c r="A45" s="4" t="s">
-        <v>1381</v>
+        <v>1385</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>1397</v>
+        <v>1401</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>1398</v>
+        <v>1402</v>
       </c>
       <c r="D45" s="7" t="s">
         <v>211</v>
@@ -10513,13 +10536,13 @@
         <v>189</v>
       </c>
       <c r="F45" s="7" t="s">
-        <v>1290</v>
+        <v>1294</v>
       </c>
       <c r="G45" s="4"/>
     </row>
     <row r="46" spans="1:7" ht="20" customHeight="1">
       <c r="A46" s="5" t="s">
-        <v>1399</v>
+        <v>1403</v>
       </c>
       <c r="B46" s="5"/>
       <c r="C46" s="5"/>
@@ -10530,13 +10553,13 @@
     </row>
     <row r="47" spans="1:7" ht="26" customHeight="1">
       <c r="A47" s="4" t="s">
-        <v>1399</v>
+        <v>1403</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>1400</v>
+        <v>1404</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>1401</v>
+        <v>1405</v>
       </c>
       <c r="D47" s="7" t="s">
         <v>211</v>
@@ -10545,21 +10568,21 @@
         <v>212</v>
       </c>
       <c r="F47" s="7" t="s">
-        <v>1402</v>
+        <v>1406</v>
       </c>
       <c r="G47" s="4" t="s">
-        <v>1403</v>
+        <v>1407</v>
       </c>
     </row>
     <row r="48" spans="1:7" ht="26" customHeight="1">
       <c r="A48" s="4" t="s">
-        <v>1399</v>
+        <v>1403</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>1404</v>
+        <v>1408</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>1405</v>
+        <v>1409</v>
       </c>
       <c r="D48" s="7" t="s">
         <v>193</v>
@@ -10568,21 +10591,21 @@
         <v>189</v>
       </c>
       <c r="F48" s="7" t="s">
-        <v>1406</v>
+        <v>1410</v>
       </c>
       <c r="G48" s="4" t="s">
-        <v>1407</v>
+        <v>1411</v>
       </c>
     </row>
     <row r="49" spans="1:7" ht="26" customHeight="1">
       <c r="A49" s="4" t="s">
-        <v>1399</v>
+        <v>1403</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>1408</v>
+        <v>1412</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>1409</v>
+        <v>1413</v>
       </c>
       <c r="D49" s="7" t="s">
         <v>818</v>
@@ -10594,7 +10617,7 @@
         <v>818</v>
       </c>
       <c r="G49" s="4" t="s">
-        <v>1410</v>
+        <v>1414</v>
       </c>
     </row>
   </sheetData>
@@ -10647,7 +10670,7 @@
     </row>
     <row r="3" spans="1:6" ht="22" customHeight="1">
       <c r="A3" s="5" t="s">
-        <v>1411</v>
+        <v>1415</v>
       </c>
       <c r="B3" s="5"/>
       <c r="C3" s="5"/>
@@ -10657,19 +10680,19 @@
     </row>
     <row r="4" spans="1:6" ht="32" customHeight="1">
       <c r="A4" s="6" t="s">
-        <v>962</v>
+        <v>966</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>1412</v>
+        <v>1416</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>207</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>1413</v>
+        <v>1417</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>1414</v>
+        <v>1418</v>
       </c>
       <c r="F4" s="6" t="s">
         <v>301</v>
@@ -10677,7 +10700,7 @@
     </row>
     <row r="5" spans="1:6" ht="18" customHeight="1">
       <c r="A5" s="9" t="s">
-        <v>1415</v>
+        <v>1419</v>
       </c>
       <c r="B5" s="9"/>
       <c r="C5" s="9"/>
@@ -10687,13 +10710,13 @@
     </row>
     <row r="6" spans="1:6" ht="26" customHeight="1">
       <c r="A6" s="4" t="s">
-        <v>1415</v>
+        <v>1419</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>1416</v>
+        <v>1420</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>1417</v>
+        <v>1421</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>197</v>
@@ -10702,52 +10725,52 @@
         <v>195</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>1418</v>
+        <v>1422</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="26" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>1415</v>
+        <v>1419</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>1419</v>
+        <v>1423</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>1420</v>
+        <v>1424</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>1421</v>
+        <v>1425</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>1102</v>
+        <v>1106</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>1422</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="26" customHeight="1">
       <c r="A8" s="4" t="s">
-        <v>1415</v>
+        <v>1419</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>1423</v>
+        <v>1427</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>1424</v>
+        <v>1428</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>1186</v>
+        <v>1190</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>1425</v>
+        <v>1429</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>1426</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="18" customHeight="1">
       <c r="A9" s="9" t="s">
-        <v>1427</v>
+        <v>1431</v>
       </c>
       <c r="B9" s="9"/>
       <c r="C9" s="9"/>
@@ -10757,47 +10780,47 @@
     </row>
     <row r="10" spans="1:6" ht="26" customHeight="1">
       <c r="A10" s="4" t="s">
-        <v>1427</v>
+        <v>1431</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>1428</v>
+        <v>1432</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>1429</v>
+        <v>1433</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>1185</v>
+        <v>1189</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>1186</v>
+        <v>1190</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>1430</v>
+        <v>1434</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="26" customHeight="1">
       <c r="A11" s="4" t="s">
-        <v>1427</v>
+        <v>1431</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>1431</v>
+        <v>1435</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>1432</v>
+        <v>1436</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>1189</v>
+        <v>1193</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>1190</v>
+        <v>1194</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>1433</v>
+        <v>1437</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="18" customHeight="1">
       <c r="A12" s="9" t="s">
-        <v>1434</v>
+        <v>1438</v>
       </c>
       <c r="B12" s="9"/>
       <c r="C12" s="9"/>
@@ -10807,45 +10830,45 @@
     </row>
     <row r="13" spans="1:6" ht="26" customHeight="1">
       <c r="A13" s="4" t="s">
-        <v>1434</v>
+        <v>1438</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>1435</v>
+        <v>1439</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>842</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>1436</v>
+        <v>1440</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>1437</v>
+        <v>1441</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>1438</v>
+        <v>1442</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="26" customHeight="1">
       <c r="A14" s="4" t="s">
-        <v>1434</v>
+        <v>1438</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>1439</v>
+        <v>1443</v>
       </c>
       <c r="C14" s="4" t="s">
         <v>842</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>1440</v>
+        <v>1444</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>1441</v>
+        <v>1445</v>
       </c>
       <c r="F14" s="4"/>
     </row>
     <row r="15" spans="1:6" ht="18" customHeight="1">
       <c r="A15" s="9" t="s">
-        <v>1442</v>
+        <v>1446</v>
       </c>
       <c r="B15" s="9"/>
       <c r="C15" s="9"/>
@@ -10855,27 +10878,27 @@
     </row>
     <row r="16" spans="1:6" ht="26" customHeight="1">
       <c r="A16" s="4" t="s">
-        <v>1442</v>
+        <v>1446</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="C16" s="4" t="s">
         <v>842</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>1444</v>
+        <v>1448</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>1445</v>
+        <v>1449</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>1446</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="18" customHeight="1">
       <c r="A17" s="9" t="s">
-        <v>1447</v>
+        <v>1451</v>
       </c>
       <c r="B17" s="9"/>
       <c r="C17" s="9"/>
@@ -10885,67 +10908,67 @@
     </row>
     <row r="18" spans="1:6" ht="26" customHeight="1">
       <c r="A18" s="4" t="s">
-        <v>1447</v>
+        <v>1451</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>1448</v>
+        <v>1452</v>
       </c>
       <c r="C18" s="4" t="s">
         <v>842</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>1189</v>
+        <v>1193</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>1449</v>
+        <v>1453</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>1450</v>
+        <v>1454</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="26" customHeight="1">
       <c r="A19" s="4" t="s">
-        <v>1447</v>
+        <v>1451</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>1451</v>
+        <v>1455</v>
       </c>
       <c r="C19" s="4" t="s">
         <v>842</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>1444</v>
+        <v>1448</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>1452</v>
+        <v>1456</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>1453</v>
+        <v>1457</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="26" customHeight="1">
       <c r="A20" s="4" t="s">
-        <v>1447</v>
+        <v>1451</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>1454</v>
+        <v>1458</v>
       </c>
       <c r="C20" s="4" t="s">
         <v>842</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>1455</v>
+        <v>1459</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>1456</v>
+        <v>1460</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>1457</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="18" customHeight="1">
       <c r="A21" s="9" t="s">
-        <v>1458</v>
+        <v>1462</v>
       </c>
       <c r="B21" s="9"/>
       <c r="C21" s="9"/>
@@ -10955,27 +10978,27 @@
     </row>
     <row r="22" spans="1:6" ht="26" customHeight="1">
       <c r="A22" s="4" t="s">
-        <v>1458</v>
+        <v>1462</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>1459</v>
+        <v>1463</v>
       </c>
       <c r="C22" s="4" t="s">
         <v>842</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>1460</v>
+        <v>1464</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>1461</v>
+        <v>1465</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>1462</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="24" spans="1:6">
       <c r="A24" s="13" t="s">
-        <v>1463</v>
+        <v>1467</v>
       </c>
       <c r="B24" s="13"/>
       <c r="C24" s="13"/>
@@ -11026,362 +11049,362 @@
     </row>
     <row r="3" spans="1:3" ht="22" customHeight="1">
       <c r="A3" s="5" t="s">
-        <v>1464</v>
+        <v>1468</v>
       </c>
       <c r="B3" s="5"/>
       <c r="C3" s="5"/>
     </row>
     <row r="4" spans="1:3" ht="32" customHeight="1">
       <c r="A4" s="6" t="s">
-        <v>962</v>
+        <v>966</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>1465</v>
+        <v>1469</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>1466</v>
+        <v>1470</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="18" customHeight="1">
       <c r="A5" s="9" t="s">
-        <v>1467</v>
+        <v>1471</v>
       </c>
       <c r="B5" s="9"/>
       <c r="C5" s="9"/>
     </row>
     <row r="6" spans="1:3" ht="26" customHeight="1">
       <c r="A6" s="4" t="s">
-        <v>1467</v>
+        <v>1471</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>1468</v>
+        <v>1472</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>1469</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="26" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>1467</v>
+        <v>1471</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>1470</v>
+        <v>1474</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>1469</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="26" customHeight="1">
       <c r="A8" s="4" t="s">
-        <v>1467</v>
+        <v>1471</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>1471</v>
+        <v>1475</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>1469</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="26" customHeight="1">
       <c r="A9" s="4" t="s">
-        <v>1467</v>
+        <v>1471</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>1472</v>
+        <v>1476</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>1469</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="18" customHeight="1">
       <c r="A10" s="9" t="s">
-        <v>1473</v>
+        <v>1477</v>
       </c>
       <c r="B10" s="9"/>
       <c r="C10" s="9"/>
     </row>
     <row r="11" spans="1:3" ht="26" customHeight="1">
       <c r="A11" s="4" t="s">
+        <v>1477</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>1478</v>
+      </c>
+      <c r="C11" s="14" t="s">
         <v>1473</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>1474</v>
-      </c>
-      <c r="C11" s="14" t="s">
-        <v>1469</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="26" customHeight="1">
       <c r="A12" s="4" t="s">
+        <v>1477</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>1479</v>
+      </c>
+      <c r="C12" s="14" t="s">
         <v>1473</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>1475</v>
-      </c>
-      <c r="C12" s="14" t="s">
-        <v>1469</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="26" customHeight="1">
       <c r="A13" s="4" t="s">
+        <v>1477</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>1480</v>
+      </c>
+      <c r="C13" s="14" t="s">
         <v>1473</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>1476</v>
-      </c>
-      <c r="C13" s="14" t="s">
-        <v>1469</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="26" customHeight="1">
       <c r="A14" s="4" t="s">
+        <v>1477</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>1481</v>
+      </c>
+      <c r="C14" s="14" t="s">
         <v>1473</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>1477</v>
-      </c>
-      <c r="C14" s="14" t="s">
-        <v>1469</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="18" customHeight="1">
       <c r="A15" s="9" t="s">
-        <v>1478</v>
+        <v>1482</v>
       </c>
       <c r="B15" s="9"/>
       <c r="C15" s="9"/>
     </row>
     <row r="16" spans="1:3" ht="26" customHeight="1">
       <c r="A16" s="4" t="s">
-        <v>1478</v>
+        <v>1482</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>1479</v>
+        <v>1483</v>
       </c>
       <c r="C16" s="14" t="s">
-        <v>1469</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="26" customHeight="1">
       <c r="A17" s="4" t="s">
-        <v>1478</v>
+        <v>1482</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>1480</v>
+        <v>1484</v>
       </c>
       <c r="C17" s="14" t="s">
-        <v>1469</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="26" customHeight="1">
       <c r="A18" s="4" t="s">
-        <v>1478</v>
+        <v>1482</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>1481</v>
+        <v>1485</v>
       </c>
       <c r="C18" s="14" t="s">
-        <v>1469</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="26" customHeight="1">
       <c r="A19" s="4" t="s">
-        <v>1478</v>
+        <v>1482</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>1482</v>
+        <v>1486</v>
       </c>
       <c r="C19" s="14" t="s">
-        <v>1469</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="18" customHeight="1">
       <c r="A20" s="9" t="s">
-        <v>1483</v>
+        <v>1487</v>
       </c>
       <c r="B20" s="9"/>
       <c r="C20" s="9"/>
     </row>
     <row r="21" spans="1:3" ht="26" customHeight="1">
       <c r="A21" s="4" t="s">
-        <v>1483</v>
+        <v>1487</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>1484</v>
+        <v>1488</v>
       </c>
       <c r="C21" s="14" t="s">
-        <v>1469</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="26" customHeight="1">
       <c r="A22" s="4" t="s">
-        <v>1483</v>
+        <v>1487</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>1485</v>
+        <v>1489</v>
       </c>
       <c r="C22" s="14" t="s">
-        <v>1469</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="26" customHeight="1">
       <c r="A23" s="4" t="s">
-        <v>1483</v>
+        <v>1487</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>1486</v>
+        <v>1490</v>
       </c>
       <c r="C23" s="14" t="s">
-        <v>1469</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="18" customHeight="1">
       <c r="A24" s="9" t="s">
-        <v>1487</v>
+        <v>1491</v>
       </c>
       <c r="B24" s="9"/>
       <c r="C24" s="9"/>
     </row>
     <row r="25" spans="1:3" ht="26" customHeight="1">
       <c r="A25" s="4" t="s">
-        <v>1487</v>
+        <v>1491</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>1488</v>
+        <v>1492</v>
       </c>
       <c r="C25" s="14" t="s">
-        <v>1469</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="26" customHeight="1">
       <c r="A26" s="4" t="s">
-        <v>1487</v>
+        <v>1491</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>1489</v>
+        <v>1493</v>
       </c>
       <c r="C26" s="14" t="s">
-        <v>1469</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="26" customHeight="1">
       <c r="A27" s="4" t="s">
-        <v>1487</v>
+        <v>1491</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>1490</v>
+        <v>1494</v>
       </c>
       <c r="C27" s="14" t="s">
-        <v>1469</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="18" customHeight="1">
       <c r="A28" s="9" t="s">
-        <v>1491</v>
+        <v>1495</v>
       </c>
       <c r="B28" s="9"/>
       <c r="C28" s="9"/>
     </row>
     <row r="29" spans="1:3" ht="26" customHeight="1">
       <c r="A29" s="4" t="s">
-        <v>1491</v>
+        <v>1495</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>1492</v>
+        <v>1496</v>
       </c>
       <c r="C29" s="14" t="s">
-        <v>1469</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="26" customHeight="1">
       <c r="A30" s="4" t="s">
-        <v>1491</v>
+        <v>1495</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>1493</v>
+        <v>1497</v>
       </c>
       <c r="C30" s="14" t="s">
-        <v>1469</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="26" customHeight="1">
       <c r="A31" s="4" t="s">
-        <v>1491</v>
+        <v>1495</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>1494</v>
+        <v>1498</v>
       </c>
       <c r="C31" s="14" t="s">
-        <v>1469</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="26" customHeight="1">
       <c r="A32" s="4" t="s">
-        <v>1491</v>
+        <v>1495</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>1495</v>
+        <v>1499</v>
       </c>
       <c r="C32" s="14" t="s">
-        <v>1469</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="18" customHeight="1">
       <c r="A33" s="9" t="s">
-        <v>1496</v>
+        <v>1500</v>
       </c>
       <c r="B33" s="9"/>
       <c r="C33" s="9"/>
     </row>
     <row r="34" spans="1:3" ht="26" customHeight="1">
       <c r="A34" s="4" t="s">
-        <v>1496</v>
+        <v>1500</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>1497</v>
+        <v>1501</v>
       </c>
       <c r="C34" s="14" t="s">
-        <v>1469</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="26" customHeight="1">
       <c r="A35" s="4" t="s">
-        <v>1496</v>
+        <v>1500</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>1498</v>
+        <v>1502</v>
       </c>
       <c r="C35" s="14" t="s">
-        <v>1469</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="18" customHeight="1">
       <c r="A36" s="9" t="s">
-        <v>1499</v>
+        <v>1503</v>
       </c>
       <c r="B36" s="9"/>
       <c r="C36" s="9"/>
     </row>
     <row r="37" spans="1:3" ht="26" customHeight="1">
       <c r="A37" s="4" t="s">
-        <v>1499</v>
+        <v>1503</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>1500</v>
+        <v>1504</v>
       </c>
       <c r="C37" s="14" t="s">
-        <v>1469</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="38" spans="1:3" ht="26" customHeight="1">
       <c r="A38" s="4" t="s">
-        <v>1499</v>
+        <v>1503</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>1501</v>
+        <v>1505</v>
       </c>
       <c r="C38" s="14" t="s">
-        <v>1469</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="39" spans="1:3" ht="18" customHeight="1">
@@ -11396,10 +11419,10 @@
         <v>364</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>1502</v>
+        <v>1506</v>
       </c>
       <c r="C40" s="14" t="s">
-        <v>1469</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="41" spans="1:3" ht="26" customHeight="1">
@@ -11407,10 +11430,10 @@
         <v>364</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>1503</v>
+        <v>1507</v>
       </c>
       <c r="C41" s="14" t="s">
-        <v>1469</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="42" spans="1:3" ht="26" customHeight="1">
@@ -11418,68 +11441,68 @@
         <v>364</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>1504</v>
+        <v>1508</v>
       </c>
       <c r="C42" s="14" t="s">
-        <v>1469</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="43" spans="1:3" ht="18" customHeight="1">
       <c r="A43" s="9" t="s">
-        <v>1505</v>
+        <v>1509</v>
       </c>
       <c r="B43" s="9"/>
       <c r="C43" s="9"/>
     </row>
     <row r="44" spans="1:3" ht="26" customHeight="1">
       <c r="A44" s="4" t="s">
-        <v>1505</v>
+        <v>1509</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>1506</v>
+        <v>1510</v>
       </c>
       <c r="C44" s="14" t="s">
-        <v>1469</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="45" spans="1:3" ht="26" customHeight="1">
       <c r="A45" s="4" t="s">
-        <v>1505</v>
+        <v>1509</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>1507</v>
+        <v>1511</v>
       </c>
       <c r="C45" s="14" t="s">
-        <v>1469</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="46" spans="1:3" ht="18" customHeight="1">
       <c r="A46" s="9" t="s">
-        <v>1508</v>
+        <v>1512</v>
       </c>
       <c r="B46" s="9"/>
       <c r="C46" s="9"/>
     </row>
     <row r="47" spans="1:3" ht="26" customHeight="1">
       <c r="A47" s="4" t="s">
-        <v>1508</v>
+        <v>1512</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>1509</v>
+        <v>1513</v>
       </c>
       <c r="C47" s="14" t="s">
-        <v>1469</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="48" spans="1:3" ht="26" customHeight="1">
       <c r="A48" s="4" t="s">
-        <v>1508</v>
+        <v>1512</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>1510</v>
+        <v>1514</v>
       </c>
       <c r="C48" s="14" t="s">
-        <v>1469</v>
+        <v>1473</v>
       </c>
     </row>
   </sheetData>
@@ -11532,7 +11555,7 @@
     </row>
     <row r="3" spans="1:4" ht="22" customHeight="1">
       <c r="A3" s="5" t="s">
-        <v>1511</v>
+        <v>1515</v>
       </c>
       <c r="B3" s="5"/>
       <c r="C3" s="5"/>
@@ -11540,21 +11563,21 @@
     </row>
     <row r="4" spans="1:4" ht="32" customHeight="1">
       <c r="A4" s="6" t="s">
-        <v>1512</v>
+        <v>1516</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>223</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>1513</v>
+        <v>1517</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>1514</v>
+        <v>1518</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="18" customHeight="1">
       <c r="A5" s="9" t="s">
-        <v>967</v>
+        <v>971</v>
       </c>
       <c r="B5" s="9"/>
       <c r="C5" s="9"/>
@@ -11562,63 +11585,63 @@
     </row>
     <row r="6" spans="1:4" ht="24" customHeight="1">
       <c r="A6" s="4" t="s">
-        <v>967</v>
+        <v>971</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>1515</v>
+        <v>1519</v>
       </c>
       <c r="C6" s="18" t="s">
-        <v>1516</v>
+        <v>1520</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>1517</v>
+        <v>1521</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="24" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>967</v>
+        <v>971</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>1518</v>
+        <v>1522</v>
       </c>
       <c r="C7" s="18" t="s">
-        <v>1516</v>
+        <v>1520</v>
       </c>
       <c r="D7" s="14" t="s">
-        <v>1519</v>
+        <v>1523</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="24" customHeight="1">
       <c r="A8" s="4" t="s">
-        <v>967</v>
+        <v>971</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>1520</v>
+        <v>1524</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>1521</v>
+        <v>1525</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>1522</v>
+        <v>1526</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="24" customHeight="1">
       <c r="A9" s="4" t="s">
-        <v>967</v>
+        <v>971</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>1523</v>
+        <v>1527</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>1524</v>
+        <v>1528</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>1525</v>
+        <v>1529</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="18" customHeight="1">
       <c r="A10" s="9" t="s">
-        <v>1526</v>
+        <v>1530</v>
       </c>
       <c r="B10" s="9"/>
       <c r="C10" s="9"/>
@@ -11626,35 +11649,35 @@
     </row>
     <row r="11" spans="1:4" ht="24" customHeight="1">
       <c r="A11" s="4" t="s">
-        <v>1526</v>
+        <v>1530</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>1527</v>
+        <v>1531</v>
       </c>
       <c r="C11" s="18" t="s">
-        <v>1516</v>
+        <v>1520</v>
       </c>
       <c r="D11" s="14" t="s">
-        <v>1528</v>
+        <v>1532</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="24" customHeight="1">
       <c r="A12" s="4" t="s">
-        <v>1526</v>
+        <v>1530</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>1529</v>
+        <v>1533</v>
       </c>
       <c r="C12" s="19" t="s">
-        <v>1521</v>
+        <v>1525</v>
       </c>
       <c r="D12" s="14" t="s">
-        <v>1530</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="18" customHeight="1">
       <c r="A13" s="9" t="s">
-        <v>1531</v>
+        <v>1535</v>
       </c>
       <c r="B13" s="9"/>
       <c r="C13" s="9"/>
@@ -11662,35 +11685,35 @@
     </row>
     <row r="14" spans="1:4" ht="24" customHeight="1">
       <c r="A14" s="4" t="s">
-        <v>1531</v>
+        <v>1535</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>1532</v>
+        <v>1536</v>
       </c>
       <c r="C14" s="18" t="s">
-        <v>1516</v>
+        <v>1520</v>
       </c>
       <c r="D14" s="14" t="s">
-        <v>1533</v>
+        <v>1537</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="24" customHeight="1">
       <c r="A15" s="4" t="s">
-        <v>1531</v>
+        <v>1535</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>1534</v>
+        <v>1538</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>1524</v>
+        <v>1528</v>
       </c>
       <c r="D15" s="14" t="s">
-        <v>1535</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="18" customHeight="1">
       <c r="A16" s="9" t="s">
-        <v>1536</v>
+        <v>1540</v>
       </c>
       <c r="B16" s="9"/>
       <c r="C16" s="9"/>
@@ -11698,49 +11721,49 @@
     </row>
     <row r="17" spans="1:4" ht="24" customHeight="1">
       <c r="A17" s="4" t="s">
-        <v>1536</v>
+        <v>1540</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>1537</v>
+        <v>1541</v>
       </c>
       <c r="C17" s="18" t="s">
-        <v>1516</v>
+        <v>1520</v>
       </c>
       <c r="D17" s="14" t="s">
-        <v>1538</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="24" customHeight="1">
       <c r="A18" s="4" t="s">
-        <v>1536</v>
+        <v>1540</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>1539</v>
+        <v>1543</v>
       </c>
       <c r="C18" s="18" t="s">
-        <v>1516</v>
+        <v>1520</v>
       </c>
       <c r="D18" s="14" t="s">
-        <v>1540</v>
+        <v>1544</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="24" customHeight="1">
       <c r="A19" s="4" t="s">
-        <v>1536</v>
+        <v>1540</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>1541</v>
+        <v>1545</v>
       </c>
       <c r="C19" s="19" t="s">
-        <v>1521</v>
+        <v>1525</v>
       </c>
       <c r="D19" s="14" t="s">
-        <v>1542</v>
+        <v>1546</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="18" customHeight="1">
       <c r="A20" s="9" t="s">
-        <v>988</v>
+        <v>992</v>
       </c>
       <c r="B20" s="9"/>
       <c r="C20" s="9"/>
@@ -11748,35 +11771,35 @@
     </row>
     <row r="21" spans="1:4" ht="24" customHeight="1">
       <c r="A21" s="4" t="s">
-        <v>988</v>
+        <v>992</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>1543</v>
+        <v>1547</v>
       </c>
       <c r="C21" s="18" t="s">
-        <v>1516</v>
+        <v>1520</v>
       </c>
       <c r="D21" s="14" t="s">
-        <v>1544</v>
+        <v>1548</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="24" customHeight="1">
       <c r="A22" s="4" t="s">
-        <v>988</v>
+        <v>992</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>1545</v>
+        <v>1549</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>1524</v>
+        <v>1528</v>
       </c>
       <c r="D22" s="14" t="s">
-        <v>1546</v>
+        <v>1550</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="18" customHeight="1">
       <c r="A23" s="9" t="s">
-        <v>995</v>
+        <v>999</v>
       </c>
       <c r="B23" s="9"/>
       <c r="C23" s="9"/>
@@ -11784,35 +11807,35 @@
     </row>
     <row r="24" spans="1:4" ht="24" customHeight="1">
       <c r="A24" s="4" t="s">
-        <v>995</v>
+        <v>999</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>1547</v>
+        <v>1551</v>
       </c>
       <c r="C24" s="18" t="s">
-        <v>1516</v>
+        <v>1520</v>
       </c>
       <c r="D24" s="14" t="s">
-        <v>1548</v>
+        <v>1552</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="24" customHeight="1">
       <c r="A25" s="4" t="s">
-        <v>995</v>
+        <v>999</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>1549</v>
+        <v>1553</v>
       </c>
       <c r="C25" s="19" t="s">
-        <v>1521</v>
+        <v>1525</v>
       </c>
       <c r="D25" s="14" t="s">
-        <v>1550</v>
+        <v>1554</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="18" customHeight="1">
       <c r="A26" s="9" t="s">
-        <v>1551</v>
+        <v>1555</v>
       </c>
       <c r="B26" s="9"/>
       <c r="C26" s="9"/>
@@ -11820,35 +11843,35 @@
     </row>
     <row r="27" spans="1:4" ht="24" customHeight="1">
       <c r="A27" s="4" t="s">
-        <v>1551</v>
+        <v>1555</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>1552</v>
+        <v>1556</v>
       </c>
       <c r="C27" s="18" t="s">
-        <v>1516</v>
+        <v>1520</v>
       </c>
       <c r="D27" s="14" t="s">
-        <v>1553</v>
+        <v>1557</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="24" customHeight="1">
       <c r="A28" s="4" t="s">
-        <v>1551</v>
+        <v>1555</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>1554</v>
+        <v>1558</v>
       </c>
       <c r="C28" s="19" t="s">
-        <v>1521</v>
+        <v>1525</v>
       </c>
       <c r="D28" s="14" t="s">
-        <v>1555</v>
+        <v>1559</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="18" customHeight="1">
       <c r="A29" s="9" t="s">
-        <v>1556</v>
+        <v>1560</v>
       </c>
       <c r="B29" s="9"/>
       <c r="C29" s="9"/>
@@ -11856,35 +11879,35 @@
     </row>
     <row r="30" spans="1:4" ht="24" customHeight="1">
       <c r="A30" s="4" t="s">
-        <v>1556</v>
+        <v>1560</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>1557</v>
+        <v>1561</v>
       </c>
       <c r="C30" s="18" t="s">
-        <v>1516</v>
+        <v>1520</v>
       </c>
       <c r="D30" s="14" t="s">
-        <v>1558</v>
+        <v>1562</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="24" customHeight="1">
       <c r="A31" s="4" t="s">
-        <v>1556</v>
+        <v>1560</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>1559</v>
+        <v>1563</v>
       </c>
       <c r="C31" s="19" t="s">
-        <v>1521</v>
+        <v>1525</v>
       </c>
       <c r="D31" s="14" t="s">
-        <v>1560</v>
+        <v>1564</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="18" customHeight="1">
       <c r="A32" s="9" t="s">
-        <v>1003</v>
+        <v>1007</v>
       </c>
       <c r="B32" s="9"/>
       <c r="C32" s="9"/>
@@ -11892,35 +11915,35 @@
     </row>
     <row r="33" spans="1:4" ht="24" customHeight="1">
       <c r="A33" s="4" t="s">
-        <v>1003</v>
+        <v>1007</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>1561</v>
+        <v>1565</v>
       </c>
       <c r="C33" s="18" t="s">
-        <v>1516</v>
+        <v>1520</v>
       </c>
       <c r="D33" s="14" t="s">
-        <v>1562</v>
+        <v>1566</v>
       </c>
     </row>
     <row r="34" spans="1:4" ht="24" customHeight="1">
       <c r="A34" s="4" t="s">
-        <v>1003</v>
+        <v>1007</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>1563</v>
+        <v>1567</v>
       </c>
       <c r="C34" s="18" t="s">
-        <v>1516</v>
+        <v>1520</v>
       </c>
       <c r="D34" s="14" t="s">
-        <v>1564</v>
+        <v>1568</v>
       </c>
     </row>
     <row r="35" spans="1:4" ht="18" customHeight="1">
       <c r="A35" s="9" t="s">
-        <v>1565</v>
+        <v>1569</v>
       </c>
       <c r="B35" s="9"/>
       <c r="C35" s="9"/>
@@ -11928,35 +11951,35 @@
     </row>
     <row r="36" spans="1:4" ht="24" customHeight="1">
       <c r="A36" s="4" t="s">
-        <v>1565</v>
+        <v>1569</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>1566</v>
+        <v>1570</v>
       </c>
       <c r="C36" s="18" t="s">
-        <v>1516</v>
+        <v>1520</v>
       </c>
       <c r="D36" s="14" t="s">
-        <v>1567</v>
+        <v>1571</v>
       </c>
     </row>
     <row r="37" spans="1:4" ht="24" customHeight="1">
       <c r="A37" s="4" t="s">
-        <v>1565</v>
+        <v>1569</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>1568</v>
+        <v>1572</v>
       </c>
       <c r="C37" s="19" t="s">
-        <v>1521</v>
+        <v>1525</v>
       </c>
       <c r="D37" s="14" t="s">
-        <v>1569</v>
+        <v>1573</v>
       </c>
     </row>
     <row r="38" spans="1:4" ht="18" customHeight="1">
       <c r="A38" s="9" t="s">
-        <v>1007</v>
+        <v>1011</v>
       </c>
       <c r="B38" s="9"/>
       <c r="C38" s="9"/>
@@ -11964,35 +11987,35 @@
     </row>
     <row r="39" spans="1:4" ht="24" customHeight="1">
       <c r="A39" s="4" t="s">
-        <v>1007</v>
+        <v>1011</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>1570</v>
+        <v>1574</v>
       </c>
       <c r="C39" s="18" t="s">
-        <v>1516</v>
+        <v>1520</v>
       </c>
       <c r="D39" s="14" t="s">
-        <v>1571</v>
+        <v>1575</v>
       </c>
     </row>
     <row r="40" spans="1:4" ht="24" customHeight="1">
       <c r="A40" s="4" t="s">
-        <v>1007</v>
+        <v>1011</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>1572</v>
+        <v>1576</v>
       </c>
       <c r="C40" s="19" t="s">
-        <v>1521</v>
+        <v>1525</v>
       </c>
       <c r="D40" s="14" t="s">
-        <v>1573</v>
+        <v>1577</v>
       </c>
     </row>
     <row r="41" spans="1:4" ht="18" customHeight="1">
       <c r="A41" s="9" t="s">
-        <v>1574</v>
+        <v>1578</v>
       </c>
       <c r="B41" s="9"/>
       <c r="C41" s="9"/>
@@ -12000,35 +12023,35 @@
     </row>
     <row r="42" spans="1:4" ht="24" customHeight="1">
       <c r="A42" s="4" t="s">
-        <v>1574</v>
+        <v>1578</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>1575</v>
+        <v>1579</v>
       </c>
       <c r="C42" s="18" t="s">
-        <v>1516</v>
+        <v>1520</v>
       </c>
       <c r="D42" s="14" t="s">
-        <v>1576</v>
+        <v>1580</v>
       </c>
     </row>
     <row r="43" spans="1:4" ht="24" customHeight="1">
       <c r="A43" s="4" t="s">
-        <v>1574</v>
+        <v>1578</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>1577</v>
+        <v>1581</v>
       </c>
       <c r="C43" s="19" t="s">
-        <v>1521</v>
+        <v>1525</v>
       </c>
       <c r="D43" s="14" t="s">
-        <v>1578</v>
+        <v>1582</v>
       </c>
     </row>
     <row r="44" spans="1:4" ht="18" customHeight="1">
       <c r="A44" s="9" t="s">
-        <v>1579</v>
+        <v>1583</v>
       </c>
       <c r="B44" s="9"/>
       <c r="C44" s="9"/>
@@ -12036,49 +12059,49 @@
     </row>
     <row r="45" spans="1:4" ht="24" customHeight="1">
       <c r="A45" s="4" t="s">
-        <v>1579</v>
+        <v>1583</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>1580</v>
+        <v>1584</v>
       </c>
       <c r="C45" s="18" t="s">
-        <v>1516</v>
+        <v>1520</v>
       </c>
       <c r="D45" s="14" t="s">
-        <v>1581</v>
+        <v>1585</v>
       </c>
     </row>
     <row r="46" spans="1:4" ht="24" customHeight="1">
       <c r="A46" s="4" t="s">
-        <v>1579</v>
+        <v>1583</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>1582</v>
+        <v>1586</v>
       </c>
       <c r="C46" s="7" t="s">
-        <v>1524</v>
+        <v>1528</v>
       </c>
       <c r="D46" s="14" t="s">
-        <v>1583</v>
+        <v>1587</v>
       </c>
     </row>
     <row r="47" spans="1:4" ht="24" customHeight="1">
       <c r="A47" s="4" t="s">
-        <v>1579</v>
+        <v>1583</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>1584</v>
+        <v>1588</v>
       </c>
       <c r="C47" s="19" t="s">
-        <v>1521</v>
+        <v>1525</v>
       </c>
       <c r="D47" s="14" t="s">
-        <v>1585</v>
+        <v>1589</v>
       </c>
     </row>
     <row r="48" spans="1:4" ht="18" customHeight="1">
       <c r="A48" s="9" t="s">
-        <v>1586</v>
+        <v>1590</v>
       </c>
       <c r="B48" s="9"/>
       <c r="C48" s="9"/>
@@ -12086,49 +12109,49 @@
     </row>
     <row r="49" spans="1:4" ht="24" customHeight="1">
       <c r="A49" s="4" t="s">
-        <v>1586</v>
+        <v>1590</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>1587</v>
+        <v>1591</v>
       </c>
       <c r="C49" s="18" t="s">
-        <v>1516</v>
+        <v>1520</v>
       </c>
       <c r="D49" s="14" t="s">
-        <v>1588</v>
+        <v>1592</v>
       </c>
     </row>
     <row r="50" spans="1:4" ht="24" customHeight="1">
       <c r="A50" s="4" t="s">
-        <v>1586</v>
+        <v>1590</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>1589</v>
+        <v>1593</v>
       </c>
       <c r="C50" s="19" t="s">
-        <v>1521</v>
+        <v>1525</v>
       </c>
       <c r="D50" s="14" t="s">
-        <v>1590</v>
+        <v>1594</v>
       </c>
     </row>
     <row r="51" spans="1:4" ht="24" customHeight="1">
       <c r="A51" s="4" t="s">
-        <v>1586</v>
+        <v>1590</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>1591</v>
+        <v>1595</v>
       </c>
       <c r="C51" s="18" t="s">
-        <v>1516</v>
+        <v>1520</v>
       </c>
       <c r="D51" s="14" t="s">
-        <v>1592</v>
+        <v>1596</v>
       </c>
     </row>
     <row r="52" spans="1:4" ht="18" customHeight="1">
       <c r="A52" s="9" t="s">
-        <v>1593</v>
+        <v>1597</v>
       </c>
       <c r="B52" s="9"/>
       <c r="C52" s="9"/>
@@ -12136,35 +12159,35 @@
     </row>
     <row r="53" spans="1:4" ht="24" customHeight="1">
       <c r="A53" s="4" t="s">
-        <v>1593</v>
+        <v>1597</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>1594</v>
+        <v>1598</v>
       </c>
       <c r="C53" s="18" t="s">
-        <v>1516</v>
+        <v>1520</v>
       </c>
       <c r="D53" s="14" t="s">
-        <v>1595</v>
+        <v>1599</v>
       </c>
     </row>
     <row r="54" spans="1:4" ht="24" customHeight="1">
       <c r="A54" s="4" t="s">
-        <v>1593</v>
+        <v>1597</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>1596</v>
+        <v>1600</v>
       </c>
       <c r="C54" s="19" t="s">
-        <v>1521</v>
+        <v>1525</v>
       </c>
       <c r="D54" s="14" t="s">
-        <v>1597</v>
+        <v>1601</v>
       </c>
     </row>
     <row r="55" spans="1:4" ht="18" customHeight="1">
       <c r="A55" s="9" t="s">
-        <v>1598</v>
+        <v>1602</v>
       </c>
       <c r="B55" s="9"/>
       <c r="C55" s="9"/>
@@ -12172,30 +12195,30 @@
     </row>
     <row r="56" spans="1:4" ht="24" customHeight="1">
       <c r="A56" s="4" t="s">
-        <v>1598</v>
+        <v>1602</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>1599</v>
+        <v>1603</v>
       </c>
       <c r="C56" s="19" t="s">
-        <v>1521</v>
+        <v>1525</v>
       </c>
       <c r="D56" s="14" t="s">
-        <v>1600</v>
+        <v>1604</v>
       </c>
     </row>
     <row r="57" spans="1:4" ht="24" customHeight="1">
       <c r="A57" s="4" t="s">
-        <v>1598</v>
+        <v>1602</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>1601</v>
+        <v>1605</v>
       </c>
       <c r="C57" s="19" t="s">
-        <v>1521</v>
+        <v>1525</v>
       </c>
       <c r="D57" s="14" t="s">
-        <v>1602</v>
+        <v>1606</v>
       </c>
     </row>
   </sheetData>
@@ -12586,7 +12609,7 @@
     </row>
     <row r="3" spans="1:8" ht="22" customHeight="1">
       <c r="A3" s="5" t="s">
-        <v>1603</v>
+        <v>1607</v>
       </c>
       <c r="B3" s="5"/>
       <c r="C3" s="5"/>
@@ -12607,19 +12630,19 @@
         <v>596</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>1604</v>
+        <v>1608</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>1605</v>
+        <v>1609</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>1606</v>
+        <v>1610</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>1607</v>
+        <v>1611</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>1608</v>
+        <v>1612</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="24" customHeight="1">
@@ -12633,16 +12656,16 @@
         <v>613</v>
       </c>
       <c r="D5" s="14" t="s">
-        <v>1609</v>
+        <v>1613</v>
       </c>
       <c r="E5" s="14" t="s">
-        <v>1610</v>
+        <v>1614</v>
       </c>
       <c r="F5" s="14" t="s">
-        <v>1610</v>
+        <v>1614</v>
       </c>
       <c r="G5" s="14" t="s">
-        <v>1610</v>
+        <v>1614</v>
       </c>
       <c r="H5" s="11">
         <v>25</v>
@@ -12653,22 +12676,22 @@
         <v>628</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>1611</v>
+        <v>1615</v>
       </c>
       <c r="C6" s="7" t="s">
         <v>613</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>1609</v>
+        <v>1613</v>
       </c>
       <c r="E6" s="14" t="s">
-        <v>1610</v>
+        <v>1614</v>
       </c>
       <c r="F6" s="14" t="s">
-        <v>1610</v>
+        <v>1614</v>
       </c>
       <c r="G6" s="14" t="s">
-        <v>1610</v>
+        <v>1614</v>
       </c>
       <c r="H6" s="11">
         <v>48</v>
@@ -12679,22 +12702,22 @@
         <v>688</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>1612</v>
+        <v>1616</v>
       </c>
       <c r="C7" s="7" t="s">
         <v>648</v>
       </c>
       <c r="D7" s="14" t="s">
-        <v>1609</v>
+        <v>1613</v>
       </c>
       <c r="E7" s="14" t="s">
-        <v>1610</v>
+        <v>1614</v>
       </c>
       <c r="F7" s="14" t="s">
-        <v>1610</v>
+        <v>1614</v>
       </c>
       <c r="G7" s="14" t="s">
-        <v>1610</v>
+        <v>1614</v>
       </c>
       <c r="H7" s="11">
         <v>18</v>
@@ -12705,22 +12728,22 @@
         <v>695</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>1613</v>
+        <v>1617</v>
       </c>
       <c r="C8" s="7" t="s">
         <v>648</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>1609</v>
+        <v>1613</v>
       </c>
       <c r="E8" s="14" t="s">
-        <v>1610</v>
+        <v>1614</v>
       </c>
       <c r="F8" s="14" t="s">
-        <v>1610</v>
+        <v>1614</v>
       </c>
       <c r="G8" s="14" t="s">
-        <v>1610</v>
+        <v>1614</v>
       </c>
       <c r="H8" s="11">
         <v>54</v>
@@ -12731,22 +12754,22 @@
         <v>711</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>1614</v>
+        <v>1618</v>
       </c>
       <c r="C9" s="7" t="s">
         <v>613</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>1609</v>
+        <v>1613</v>
       </c>
       <c r="E9" s="14" t="s">
-        <v>1610</v>
+        <v>1614</v>
       </c>
       <c r="F9" s="14" t="s">
-        <v>1610</v>
+        <v>1614</v>
       </c>
       <c r="G9" s="14" t="s">
-        <v>1610</v>
+        <v>1614</v>
       </c>
       <c r="H9" s="11">
         <v>27</v>
@@ -12757,22 +12780,22 @@
         <v>717</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>1539</v>
+        <v>1543</v>
       </c>
       <c r="C10" s="7" t="s">
         <v>648</v>
       </c>
       <c r="D10" s="14" t="s">
-        <v>1609</v>
+        <v>1613</v>
       </c>
       <c r="E10" s="14" t="s">
-        <v>1610</v>
+        <v>1614</v>
       </c>
       <c r="F10" s="14" t="s">
-        <v>1610</v>
+        <v>1614</v>
       </c>
       <c r="G10" s="14" t="s">
-        <v>1610</v>
+        <v>1614</v>
       </c>
       <c r="H10" s="11">
         <v>39</v>
@@ -12783,22 +12806,22 @@
         <v>742</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>1615</v>
+        <v>1619</v>
       </c>
       <c r="C11" s="7" t="s">
         <v>676</v>
       </c>
       <c r="D11" s="14" t="s">
-        <v>1609</v>
+        <v>1613</v>
       </c>
       <c r="E11" s="14" t="s">
-        <v>1610</v>
+        <v>1614</v>
       </c>
       <c r="F11" s="14" t="s">
-        <v>1610</v>
+        <v>1614</v>
       </c>
       <c r="G11" s="14" t="s">
-        <v>1610</v>
+        <v>1614</v>
       </c>
       <c r="H11" s="11">
         <v>1250</v>
@@ -12809,22 +12832,22 @@
         <v>772</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>1616</v>
+        <v>1620</v>
       </c>
       <c r="C12" s="7" t="s">
         <v>613</v>
       </c>
       <c r="D12" s="14" t="s">
-        <v>1609</v>
+        <v>1613</v>
       </c>
       <c r="E12" s="14" t="s">
-        <v>1610</v>
+        <v>1614</v>
       </c>
       <c r="F12" s="14" t="s">
-        <v>1610</v>
+        <v>1614</v>
       </c>
       <c r="G12" s="14" t="s">
-        <v>1610</v>
+        <v>1614</v>
       </c>
       <c r="H12" s="11">
         <v>2850</v>
@@ -12835,22 +12858,22 @@
         <v>781</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>1617</v>
+        <v>1621</v>
       </c>
       <c r="C13" s="7" t="s">
         <v>783</v>
       </c>
       <c r="D13" s="14" t="s">
-        <v>1609</v>
+        <v>1613</v>
       </c>
       <c r="E13" s="14" t="s">
-        <v>1610</v>
+        <v>1614</v>
       </c>
       <c r="F13" s="14" t="s">
-        <v>1610</v>
+        <v>1614</v>
       </c>
       <c r="G13" s="14" t="s">
-        <v>1610</v>
+        <v>1614</v>
       </c>
       <c r="H13" s="11">
         <v>5000</v>
@@ -12861,22 +12884,22 @@
         <v>820</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>1618</v>
+        <v>1622</v>
       </c>
       <c r="C14" s="7" t="s">
         <v>613</v>
       </c>
       <c r="D14" s="14" t="s">
-        <v>1609</v>
+        <v>1613</v>
       </c>
       <c r="E14" s="14" t="s">
-        <v>1610</v>
+        <v>1614</v>
       </c>
       <c r="F14" s="14" t="s">
-        <v>1610</v>
+        <v>1614</v>
       </c>
       <c r="G14" s="14" t="s">
-        <v>1610</v>
+        <v>1614</v>
       </c>
       <c r="H14" s="11">
         <v>65</v>
@@ -12887,22 +12910,22 @@
         <v>878</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>1619</v>
+        <v>1623</v>
       </c>
       <c r="C15" s="7" t="s">
         <v>676</v>
       </c>
       <c r="D15" s="14" t="s">
-        <v>1609</v>
+        <v>1613</v>
       </c>
       <c r="E15" s="14" t="s">
-        <v>1610</v>
+        <v>1614</v>
       </c>
       <c r="F15" s="14" t="s">
-        <v>1610</v>
+        <v>1614</v>
       </c>
       <c r="G15" s="14" t="s">
-        <v>1610</v>
+        <v>1614</v>
       </c>
       <c r="H15" s="11">
         <v>213</v>
@@ -12913,22 +12936,22 @@
         <v>908</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>1620</v>
+        <v>1624</v>
       </c>
       <c r="C16" s="7" t="s">
         <v>676</v>
       </c>
       <c r="D16" s="14" t="s">
-        <v>1609</v>
+        <v>1613</v>
       </c>
       <c r="E16" s="14" t="s">
-        <v>1610</v>
+        <v>1614</v>
       </c>
       <c r="F16" s="14" t="s">
-        <v>1610</v>
+        <v>1614</v>
       </c>
       <c r="G16" s="14" t="s">
-        <v>1610</v>
+        <v>1614</v>
       </c>
       <c r="H16" s="11">
         <v>8500</v>
@@ -12936,7 +12959,7 @@
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="13" t="s">
-        <v>1621</v>
+        <v>1625</v>
       </c>
       <c r="B18" s="13"/>
       <c r="C18" s="13"/>
@@ -12992,7 +13015,7 @@
     </row>
     <row r="3" spans="1:6" ht="22" customHeight="1">
       <c r="A3" s="5" t="s">
-        <v>1622</v>
+        <v>1626</v>
       </c>
       <c r="B3" s="5"/>
       <c r="C3" s="5"/>
@@ -13002,19 +13025,19 @@
     </row>
     <row r="4" spans="1:6" ht="32" customHeight="1">
       <c r="A4" s="6" t="s">
-        <v>1623</v>
+        <v>1627</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>1624</v>
+        <v>1628</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>1625</v>
+        <v>1629</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>1626</v>
+        <v>1630</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>1627</v>
+        <v>1631</v>
       </c>
       <c r="F4" s="6" t="s">
         <v>301</v>
@@ -13022,13 +13045,13 @@
     </row>
     <row r="5" spans="1:6" ht="40" customHeight="1">
       <c r="A5" s="3" t="s">
-        <v>1628</v>
+        <v>1632</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>1629</v>
+        <v>1633</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>1630</v>
+        <v>1634</v>
       </c>
       <c r="D5" s="14" t="s">
         <v>614</v>
@@ -13037,18 +13060,18 @@
         <v>195</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>1631</v>
+        <v>1635</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="40" customHeight="1">
       <c r="A6" s="3" t="s">
-        <v>1632</v>
+        <v>1636</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>1633</v>
+        <v>1637</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>1634</v>
+        <v>1638</v>
       </c>
       <c r="D6" s="14" t="s">
         <v>193</v>
@@ -13057,18 +13080,18 @@
         <v>189</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>1635</v>
+        <v>1639</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="40" customHeight="1">
       <c r="A7" s="3" t="s">
-        <v>1636</v>
+        <v>1640</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>1637</v>
+        <v>1641</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>1638</v>
+        <v>1642</v>
       </c>
       <c r="D7" s="14" t="s">
         <v>189</v>
@@ -13077,18 +13100,18 @@
         <v>251</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>1639</v>
+        <v>1643</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="40" customHeight="1">
       <c r="A8" s="3" t="s">
-        <v>1640</v>
+        <v>1644</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>1641</v>
+        <v>1645</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>1642</v>
+        <v>1646</v>
       </c>
       <c r="D8" s="14" t="s">
         <v>195</v>
@@ -13097,18 +13120,18 @@
         <v>193</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>1643</v>
+        <v>1647</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="40" customHeight="1">
       <c r="A9" s="3" t="s">
-        <v>1644</v>
+        <v>1648</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>1645</v>
+        <v>1649</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>1646</v>
+        <v>1650</v>
       </c>
       <c r="D9" s="14" t="s">
         <v>193</v>
@@ -13117,12 +13140,12 @@
         <v>189</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>1647</v>
+        <v>1651</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="22" customHeight="1">
       <c r="A11" s="5" t="s">
-        <v>1648</v>
+        <v>1652</v>
       </c>
       <c r="B11" s="5"/>
       <c r="C11" s="5"/>
@@ -13132,16 +13155,16 @@
     </row>
     <row r="12" spans="1:6" ht="32" customHeight="1">
       <c r="A12" s="6" t="s">
-        <v>1279</v>
+        <v>1283</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>1649</v>
+        <v>1653</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>1284</v>
+        <v>1288</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>1650</v>
+        <v>1654</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>186</v>
@@ -13150,109 +13173,109 @@
     </row>
     <row r="13" spans="1:6" ht="24" customHeight="1">
       <c r="A13" s="3" t="s">
-        <v>1651</v>
+        <v>1655</v>
       </c>
       <c r="B13" s="14" t="s">
-        <v>1652</v>
+        <v>1656</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>1155</v>
+        <v>1159</v>
       </c>
       <c r="D13" s="14" t="s">
-        <v>1653</v>
+        <v>1657</v>
       </c>
       <c r="E13" s="14" t="s">
-        <v>1654</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="24" customHeight="1">
       <c r="A14" s="3" t="s">
-        <v>1655</v>
+        <v>1659</v>
       </c>
       <c r="B14" s="14" t="s">
-        <v>1656</v>
+        <v>1660</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>1402</v>
+        <v>1406</v>
       </c>
       <c r="D14" s="14" t="s">
-        <v>1657</v>
+        <v>1661</v>
       </c>
       <c r="E14" s="14" t="s">
-        <v>1658</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="24" customHeight="1">
       <c r="A15" s="3" t="s">
-        <v>1659</v>
+        <v>1663</v>
       </c>
       <c r="B15" s="14" t="s">
-        <v>1660</v>
+        <v>1664</v>
       </c>
       <c r="C15" s="14" t="s">
-        <v>1288</v>
+        <v>1292</v>
       </c>
       <c r="D15" s="14" t="s">
-        <v>1661</v>
+        <v>1665</v>
       </c>
       <c r="E15" s="14" t="s">
-        <v>1662</v>
+        <v>1666</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="24" customHeight="1">
       <c r="A16" s="3" t="s">
-        <v>1663</v>
+        <v>1667</v>
       </c>
       <c r="B16" s="14" t="s">
-        <v>1664</v>
+        <v>1668</v>
       </c>
       <c r="C16" s="14" t="s">
-        <v>1290</v>
+        <v>1294</v>
       </c>
       <c r="D16" s="14" t="s">
-        <v>1665</v>
+        <v>1669</v>
       </c>
       <c r="E16" s="14" t="s">
-        <v>1666</v>
+        <v>1670</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="24" customHeight="1">
       <c r="A17" s="3" t="s">
-        <v>1667</v>
+        <v>1671</v>
       </c>
       <c r="B17" s="14" t="s">
-        <v>1668</v>
+        <v>1672</v>
       </c>
       <c r="C17" s="14" t="s">
-        <v>1669</v>
+        <v>1673</v>
       </c>
       <c r="D17" s="14" t="s">
-        <v>1670</v>
+        <v>1674</v>
       </c>
       <c r="E17" s="14" t="s">
-        <v>1671</v>
+        <v>1675</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="24" customHeight="1">
       <c r="A18" s="3" t="s">
-        <v>1672</v>
+        <v>1676</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>1673</v>
+        <v>1677</v>
       </c>
       <c r="C18" s="14" t="s">
-        <v>1288</v>
+        <v>1292</v>
       </c>
       <c r="D18" s="14" t="s">
-        <v>1674</v>
+        <v>1678</v>
       </c>
       <c r="E18" s="14" t="s">
-        <v>1675</v>
+        <v>1679</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="13" t="s">
-        <v>1676</v>
+        <v>1680</v>
       </c>
       <c r="B20" s="13"/>
       <c r="C20" s="13"/>
@@ -13301,7 +13324,7 @@
     </row>
     <row r="3" spans="1:4" ht="22" customHeight="1">
       <c r="A3" s="5" t="s">
-        <v>1677</v>
+        <v>1681</v>
       </c>
       <c r="B3" s="5"/>
       <c r="C3" s="5"/>
@@ -13309,21 +13332,21 @@
     </row>
     <row r="4" spans="1:4" ht="32" customHeight="1">
       <c r="A4" s="6" t="s">
-        <v>1279</v>
+        <v>1283</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>223</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>1678</v>
+        <v>1682</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>1679</v>
+        <v>1683</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="20" customHeight="1">
       <c r="A5" s="5" t="s">
-        <v>1285</v>
+        <v>1289</v>
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="5"/>
@@ -13331,190 +13354,190 @@
     </row>
     <row r="6" spans="1:4" ht="22" customHeight="1">
       <c r="A6" s="7" t="s">
-        <v>1680</v>
+        <v>1684</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>1681</v>
+        <v>1685</v>
       </c>
       <c r="C6" s="16">
         <v>0</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>1682</v>
+        <v>1686</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="22" customHeight="1">
       <c r="A7" s="7" t="s">
-        <v>1683</v>
+        <v>1687</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>1684</v>
+        <v>1688</v>
       </c>
       <c r="C7" s="16">
         <v>0</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>1685</v>
+        <v>1689</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="22" customHeight="1">
       <c r="A8" s="7" t="s">
-        <v>1686</v>
+        <v>1690</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>1687</v>
+        <v>1691</v>
       </c>
       <c r="C8" s="16">
         <v>0</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>1688</v>
+        <v>1692</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="22" customHeight="1">
       <c r="A9" s="7" t="s">
-        <v>1689</v>
+        <v>1693</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>1690</v>
+        <v>1694</v>
       </c>
       <c r="C9" s="16">
         <v>0</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>1691</v>
+        <v>1695</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="22" customHeight="1">
       <c r="A10" s="7" t="s">
-        <v>1692</v>
+        <v>1696</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>1693</v>
+        <v>1697</v>
       </c>
       <c r="C10" s="16">
         <v>0</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>1694</v>
+        <v>1698</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="22" customHeight="1">
       <c r="A11" s="7" t="s">
-        <v>1695</v>
+        <v>1699</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>1696</v>
+        <v>1700</v>
       </c>
       <c r="C11" s="16">
         <v>0</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>1697</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="22" customHeight="1">
       <c r="A12" s="7" t="s">
-        <v>1698</v>
+        <v>1702</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>1699</v>
+        <v>1703</v>
       </c>
       <c r="C12" s="16">
         <v>0</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>1700</v>
+        <v>1704</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="22" customHeight="1">
       <c r="A13" s="7" t="s">
-        <v>1701</v>
+        <v>1705</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>1702</v>
+        <v>1706</v>
       </c>
       <c r="C13" s="16">
         <v>0</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>1703</v>
+        <v>1707</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="22" customHeight="1">
       <c r="A14" s="7" t="s">
-        <v>1704</v>
+        <v>1708</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>1705</v>
+        <v>1709</v>
       </c>
       <c r="C14" s="16">
         <v>0</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>1706</v>
+        <v>1710</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="22" customHeight="1">
       <c r="A15" s="7" t="s">
-        <v>1227</v>
+        <v>1231</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>1707</v>
+        <v>1711</v>
       </c>
       <c r="C15" s="16">
         <v>0</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>1708</v>
+        <v>1712</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="22" customHeight="1">
       <c r="A16" s="7" t="s">
-        <v>1709</v>
+        <v>1713</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>1710</v>
+        <v>1714</v>
       </c>
       <c r="C16" s="16">
         <v>0</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>1711</v>
+        <v>1715</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="22" customHeight="1">
       <c r="A17" s="7" t="s">
-        <v>1231</v>
+        <v>1235</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>1712</v>
+        <v>1716</v>
       </c>
       <c r="C17" s="16">
         <v>0</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>1713</v>
+        <v>1717</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="22" customHeight="1">
       <c r="A18" s="7" t="s">
-        <v>1714</v>
+        <v>1718</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>1715</v>
+        <v>1719</v>
       </c>
       <c r="C18" s="16">
         <v>0</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>1716</v>
+        <v>1720</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="22" customHeight="1">
       <c r="A19" s="7"/>
       <c r="B19" s="3" t="s">
-        <v>1717</v>
+        <v>1721</v>
       </c>
       <c r="C19" s="17">
         <f>SUM(C6:C18)</f>
@@ -13524,7 +13547,7 @@
     </row>
     <row r="20" spans="1:4" ht="20" customHeight="1">
       <c r="A20" s="5" t="s">
-        <v>1317</v>
+        <v>1321</v>
       </c>
       <c r="B20" s="5"/>
       <c r="C20" s="5"/>
@@ -13532,35 +13555,34 @@
     </row>
     <row r="21" spans="1:4" ht="22" customHeight="1">
       <c r="A21" s="7" t="s">
-        <v>1718</v>
+        <v>1722</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>1719</v>
+        <v>1723</v>
       </c>
       <c r="C21" s="16">
         <v>0.15</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>1720</v>
+        <v>1724</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="22" customHeight="1">
       <c r="A22" s="7"/>
       <c r="B22" s="3" t="s">
-        <v>1721</v>
+        <v>1725</v>
       </c>
       <c r="C22" s="17">
         <f>C19*C21</f>
         <v>0</v>
       </c>
-      <c r="D22" s="4">
-        <f> Direct × CDI %</f>
-        <v>0</v>
+      <c r="D22" s="4" t="s">
+        <v>1726</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="20" customHeight="1">
       <c r="A23" s="5" t="s">
-        <v>1351</v>
+        <v>1355</v>
       </c>
       <c r="B23" s="5"/>
       <c r="C23" s="5"/>
@@ -13568,35 +13590,34 @@
     </row>
     <row r="24" spans="1:4" ht="22" customHeight="1">
       <c r="A24" s="7" t="s">
-        <v>1722</v>
+        <v>1727</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>1723</v>
+        <v>1728</v>
       </c>
       <c r="C24" s="16">
         <v>0.08</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>1724</v>
+        <v>1729</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="22" customHeight="1">
       <c r="A25" s="7"/>
       <c r="B25" s="3" t="s">
-        <v>1725</v>
+        <v>1730</v>
       </c>
       <c r="C25" s="17">
         <f>C19*C24</f>
         <v>0</v>
       </c>
-      <c r="D25" s="4">
-        <f> Direct × OH %</f>
-        <v>0</v>
+      <c r="D25" s="4" t="s">
+        <v>1731</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="20" customHeight="1">
       <c r="A26" s="5" t="s">
-        <v>1359</v>
+        <v>1363</v>
       </c>
       <c r="B26" s="5"/>
       <c r="C26" s="5"/>
@@ -13604,35 +13625,34 @@
     </row>
     <row r="27" spans="1:4" ht="22" customHeight="1">
       <c r="A27" s="7" t="s">
-        <v>1726</v>
+        <v>1732</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>1727</v>
+        <v>1733</v>
       </c>
       <c r="C27" s="16">
         <v>0.03</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>1728</v>
+        <v>1734</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="22" customHeight="1">
       <c r="A28" s="7"/>
       <c r="B28" s="3" t="s">
-        <v>1729</v>
+        <v>1735</v>
       </c>
       <c r="C28" s="17">
         <f>(C19+C22+C25)*C27</f>
         <v>0</v>
       </c>
-      <c r="D28" s="4">
-        <f> (Direct + CDI + OH) × B+I %</f>
-        <v>0</v>
+      <c r="D28" s="4" t="s">
+        <v>1736</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="20" customHeight="1">
       <c r="A29" s="5" t="s">
-        <v>1381</v>
+        <v>1385</v>
       </c>
       <c r="B29" s="5"/>
       <c r="C29" s="5"/>
@@ -13640,35 +13660,34 @@
     </row>
     <row r="30" spans="1:4" ht="22" customHeight="1">
       <c r="A30" s="7" t="s">
-        <v>1730</v>
+        <v>1737</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>1731</v>
+        <v>1738</v>
       </c>
       <c r="C30" s="16">
         <v>0.12</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>1732</v>
+        <v>1739</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="22" customHeight="1">
       <c r="A31" s="7"/>
       <c r="B31" s="3" t="s">
-        <v>1733</v>
+        <v>1740</v>
       </c>
       <c r="C31" s="17">
         <f>C19*C30</f>
         <v>0</v>
       </c>
-      <c r="D31" s="4">
-        <f> Direct × Contingency %</f>
-        <v>0</v>
+      <c r="D31" s="4" t="s">
+        <v>1741</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="20" customHeight="1">
       <c r="A32" s="5" t="s">
-        <v>1399</v>
+        <v>1403</v>
       </c>
       <c r="B32" s="5"/>
       <c r="C32" s="5"/>
@@ -13676,35 +13695,34 @@
     </row>
     <row r="33" spans="1:4" ht="22" customHeight="1">
       <c r="A33" s="7" t="s">
-        <v>1734</v>
+        <v>1742</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>1735</v>
+        <v>1743</v>
       </c>
       <c r="C33" s="16">
         <v>0.1</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>1732</v>
+        <v>1739</v>
       </c>
     </row>
     <row r="34" spans="1:4" ht="22" customHeight="1">
       <c r="A34" s="7"/>
       <c r="B34" s="3" t="s">
-        <v>1736</v>
+        <v>1744</v>
       </c>
       <c r="C34" s="17">
         <f>(C19+C22+C25+C28+C31)*C33</f>
         <v>0</v>
       </c>
-      <c r="D34" s="4">
-        <f> (Direct + CDI + OH + B+I + Cont.) × Profit %</f>
-        <v>0</v>
+      <c r="D34" s="4" t="s">
+        <v>1745</v>
       </c>
     </row>
     <row r="36" spans="1:4" ht="26" customHeight="1">
       <c r="A36" s="5" t="s">
-        <v>1737</v>
+        <v>1746</v>
       </c>
       <c r="B36" s="5"/>
       <c r="C36" s="17">
@@ -13712,12 +13730,12 @@
         <v>0</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>1738</v>
+        <v>1747</v>
       </c>
     </row>
     <row r="38" spans="1:4">
       <c r="A38" s="13" t="s">
-        <v>1739</v>
+        <v>1748</v>
       </c>
       <c r="B38" s="13"/>
       <c r="C38" s="13"/>
@@ -13781,7 +13799,7 @@
     </row>
     <row r="3" spans="1:8" ht="22" customHeight="1">
       <c r="A3" s="5" t="s">
-        <v>1740</v>
+        <v>1749</v>
       </c>
       <c r="B3" s="5"/>
       <c r="C3" s="5"/>
@@ -13793,39 +13811,39 @@
     </row>
     <row r="4" spans="1:8" ht="32" customHeight="1">
       <c r="A4" s="6" t="s">
-        <v>1741</v>
+        <v>1750</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>962</v>
+        <v>966</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>1742</v>
+        <v>1751</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>1743</v>
+        <v>1752</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>1744</v>
+        <v>1753</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>1745</v>
+        <v>1754</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>1746</v>
+        <v>1755</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>1747</v>
+        <v>1756</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="30" customHeight="1">
       <c r="A5" s="3" t="s">
-        <v>1748</v>
+        <v>1757</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>1749</v>
+        <v>1758</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>1750</v>
+        <v>1759</v>
       </c>
       <c r="D5" s="7">
         <v>4</v>
@@ -13840,18 +13858,18 @@
         <v>4</v>
       </c>
       <c r="H5" s="14" t="s">
-        <v>1751</v>
+        <v>1760</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="30" customHeight="1">
       <c r="A6" s="3" t="s">
-        <v>1752</v>
+        <v>1761</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>1749</v>
+        <v>1758</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>1753</v>
+        <v>1762</v>
       </c>
       <c r="D6" s="7">
         <v>3</v>
@@ -13866,18 +13884,18 @@
         <v>6</v>
       </c>
       <c r="H6" s="14" t="s">
-        <v>1754</v>
+        <v>1763</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="30" customHeight="1">
       <c r="A7" s="3" t="s">
-        <v>1755</v>
+        <v>1764</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>1756</v>
+        <v>1765</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>1757</v>
+        <v>1766</v>
       </c>
       <c r="D7" s="7">
         <v>4</v>
@@ -13892,18 +13910,18 @@
         <v>3</v>
       </c>
       <c r="H7" s="14" t="s">
-        <v>1758</v>
+        <v>1767</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="30" customHeight="1">
       <c r="A8" s="3" t="s">
-        <v>1759</v>
+        <v>1768</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>1760</v>
+        <v>1769</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>1761</v>
+        <v>1770</v>
       </c>
       <c r="D8" s="7">
         <v>3</v>
@@ -13918,18 +13936,18 @@
         <v>0</v>
       </c>
       <c r="H8" s="14" t="s">
-        <v>1762</v>
+        <v>1771</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="30" customHeight="1">
       <c r="A9" s="3" t="s">
-        <v>1763</v>
+        <v>1772</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>1764</v>
+        <v>1773</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>1765</v>
+        <v>1774</v>
       </c>
       <c r="D9" s="7">
         <v>3</v>
@@ -13944,18 +13962,18 @@
         <v>0</v>
       </c>
       <c r="H9" s="14" t="s">
-        <v>1766</v>
+        <v>1775</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="30" customHeight="1">
       <c r="A10" s="3" t="s">
-        <v>1767</v>
+        <v>1776</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>1768</v>
+        <v>1777</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>1769</v>
+        <v>1778</v>
       </c>
       <c r="D10" s="7">
         <v>2</v>
@@ -13970,18 +13988,18 @@
         <v>4</v>
       </c>
       <c r="H10" s="14" t="s">
-        <v>1770</v>
+        <v>1779</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="30" customHeight="1">
       <c r="A11" s="3" t="s">
-        <v>1771</v>
+        <v>1780</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>1772</v>
+        <v>1781</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>1773</v>
+        <v>1782</v>
       </c>
       <c r="D11" s="7">
         <v>3</v>
@@ -13996,18 +14014,18 @@
         <v>6</v>
       </c>
       <c r="H11" s="14" t="s">
-        <v>1774</v>
+        <v>1783</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="30" customHeight="1">
       <c r="A12" s="3" t="s">
-        <v>1775</v>
+        <v>1784</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>1776</v>
+        <v>1785</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>1777</v>
+        <v>1786</v>
       </c>
       <c r="D12" s="7">
         <v>4</v>
@@ -14022,18 +14040,18 @@
         <v>4</v>
       </c>
       <c r="H12" s="14" t="s">
-        <v>1778</v>
+        <v>1787</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="30" customHeight="1">
       <c r="A13" s="3" t="s">
-        <v>1779</v>
+        <v>1788</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>1780</v>
+        <v>1789</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>1781</v>
+        <v>1790</v>
       </c>
       <c r="D13" s="7">
         <v>3</v>
@@ -14048,18 +14066,18 @@
         <v>6</v>
       </c>
       <c r="H13" s="14" t="s">
-        <v>1782</v>
+        <v>1791</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="30" customHeight="1">
       <c r="A14" s="3" t="s">
-        <v>1783</v>
+        <v>1792</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>1784</v>
+        <v>1793</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>1785</v>
+        <v>1794</v>
       </c>
       <c r="D14" s="7">
         <v>3</v>
@@ -14074,18 +14092,18 @@
         <v>6</v>
       </c>
       <c r="H14" s="14" t="s">
-        <v>1786</v>
+        <v>1795</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="30" customHeight="1">
       <c r="A15" s="3" t="s">
-        <v>1787</v>
+        <v>1796</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>1788</v>
+        <v>1797</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>1789</v>
+        <v>1798</v>
       </c>
       <c r="D15" s="7">
         <v>2</v>
@@ -14100,18 +14118,18 @@
         <v>2</v>
       </c>
       <c r="H15" s="14" t="s">
-        <v>1790</v>
+        <v>1799</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="30" customHeight="1">
       <c r="A16" s="3" t="s">
-        <v>1791</v>
+        <v>1800</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>364</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>1792</v>
+        <v>1801</v>
       </c>
       <c r="D16" s="7">
         <v>1</v>
@@ -14126,12 +14144,12 @@
         <v>8</v>
       </c>
       <c r="H16" s="14" t="s">
-        <v>1793</v>
+        <v>1802</v>
       </c>
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="13" t="s">
-        <v>1794</v>
+        <v>1803</v>
       </c>
       <c r="B18" s="13"/>
       <c r="C18" s="13"/>
@@ -14175,176 +14193,176 @@
     </row>
     <row r="3" spans="1:2" ht="22" customHeight="1">
       <c r="A3" s="5" t="s">
-        <v>1795</v>
+        <v>1804</v>
       </c>
       <c r="B3" s="5"/>
     </row>
     <row r="4" spans="1:2" ht="32" customHeight="1">
       <c r="A4" s="6" t="s">
-        <v>1796</v>
+        <v>1805</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>1797</v>
+        <v>1806</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="22" customHeight="1">
       <c r="A5" s="3" t="s">
-        <v>1798</v>
+        <v>1807</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>1799</v>
+        <v>1808</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="22" customHeight="1">
       <c r="A6" s="3" t="s">
-        <v>1800</v>
+        <v>1809</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>1801</v>
+        <v>1810</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="22" customHeight="1">
       <c r="A7" s="3" t="s">
-        <v>1802</v>
+        <v>1811</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>1803</v>
+        <v>1812</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="22" customHeight="1">
       <c r="A8" s="3" t="s">
-        <v>1804</v>
+        <v>1813</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>1805</v>
+        <v>1814</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="22" customHeight="1">
       <c r="A9" s="3" t="s">
-        <v>1806</v>
+        <v>1815</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>1807</v>
+        <v>1816</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="22" customHeight="1">
       <c r="A10" s="3" t="s">
-        <v>1808</v>
+        <v>1817</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>1809</v>
+        <v>1818</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="22" customHeight="1">
       <c r="A11" s="3" t="s">
-        <v>1810</v>
+        <v>1819</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>1811</v>
+        <v>1820</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="22" customHeight="1">
       <c r="A12" s="3" t="s">
-        <v>1812</v>
+        <v>1821</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>1813</v>
+        <v>1822</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="22" customHeight="1">
       <c r="A13" s="3" t="s">
-        <v>1814</v>
+        <v>1823</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>1815</v>
+        <v>1824</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="22" customHeight="1">
       <c r="A14" s="3" t="s">
-        <v>1816</v>
+        <v>1825</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>1817</v>
+        <v>1826</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="22" customHeight="1">
       <c r="A15" s="3" t="s">
-        <v>1818</v>
+        <v>1827</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>1819</v>
+        <v>1828</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="22" customHeight="1">
       <c r="A16" s="3" t="s">
-        <v>1820</v>
+        <v>1829</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>1821</v>
+        <v>1830</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="22" customHeight="1">
       <c r="A17" s="3" t="s">
-        <v>1822</v>
+        <v>1831</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>1823</v>
+        <v>1832</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="22" customHeight="1">
       <c r="A18" s="3" t="s">
-        <v>1824</v>
+        <v>1833</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>1825</v>
+        <v>1834</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="22" customHeight="1">
       <c r="A19" s="3" t="s">
-        <v>1826</v>
+        <v>1835</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>1827</v>
+        <v>1836</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="22" customHeight="1">
       <c r="A20" s="3" t="s">
-        <v>1828</v>
+        <v>1837</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>1829</v>
+        <v>1838</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="22" customHeight="1">
       <c r="A21" s="3" t="s">
-        <v>1830</v>
+        <v>1839</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>1831</v>
+        <v>1840</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="22" customHeight="1">
       <c r="A22" s="3" t="s">
-        <v>1832</v>
+        <v>1841</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>1833</v>
+        <v>1842</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="22" customHeight="1">
       <c r="A23" s="3" t="s">
-        <v>1834</v>
+        <v>1843</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>1835</v>
+        <v>1844</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="22" customHeight="1">
       <c r="A24" s="3" t="s">
-        <v>1836</v>
+        <v>1845</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>1837</v>
+        <v>1846</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="22" customHeight="1">
@@ -14352,47 +14370,47 @@
         <v>364</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>1838</v>
+        <v>1847</v>
       </c>
     </row>
     <row r="26" spans="1:2" ht="22" customHeight="1">
       <c r="A26" s="3" t="s">
-        <v>1839</v>
+        <v>1848</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>1840</v>
+        <v>1849</v>
       </c>
     </row>
     <row r="27" spans="1:2" ht="22" customHeight="1">
       <c r="A27" s="3" t="s">
-        <v>1841</v>
+        <v>1850</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>1842</v>
+        <v>1851</v>
       </c>
     </row>
     <row r="28" spans="1:2" ht="22" customHeight="1">
       <c r="A28" s="3" t="s">
-        <v>1843</v>
+        <v>1852</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>1844</v>
+        <v>1853</v>
       </c>
     </row>
     <row r="29" spans="1:2" ht="22" customHeight="1">
       <c r="A29" s="3" t="s">
-        <v>1845</v>
+        <v>1854</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>1846</v>
+        <v>1855</v>
       </c>
     </row>
     <row r="30" spans="1:2" ht="22" customHeight="1">
       <c r="A30" s="3" t="s">
-        <v>1847</v>
+        <v>1856</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>1848</v>
+        <v>1857</v>
       </c>
     </row>
     <row r="31" spans="1:2" ht="22" customHeight="1">
@@ -14400,87 +14418,87 @@
         <v>242</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>1849</v>
+        <v>1858</v>
       </c>
     </row>
     <row r="32" spans="1:2" ht="22" customHeight="1">
       <c r="A32" s="3" t="s">
-        <v>1850</v>
+        <v>1859</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>1851</v>
+        <v>1860</v>
       </c>
     </row>
     <row r="33" spans="1:2" ht="22" customHeight="1">
       <c r="A33" s="3" t="s">
-        <v>1852</v>
+        <v>1861</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>1853</v>
+        <v>1862</v>
       </c>
     </row>
     <row r="34" spans="1:2" ht="22" customHeight="1">
       <c r="A34" s="3" t="s">
-        <v>1854</v>
+        <v>1863</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>1855</v>
+        <v>1864</v>
       </c>
     </row>
     <row r="35" spans="1:2" ht="22" customHeight="1">
       <c r="A35" s="3" t="s">
-        <v>1856</v>
+        <v>1865</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>1857</v>
+        <v>1866</v>
       </c>
     </row>
     <row r="36" spans="1:2" ht="22" customHeight="1">
       <c r="A36" s="3" t="s">
-        <v>1858</v>
+        <v>1867</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>1859</v>
+        <v>1868</v>
       </c>
     </row>
     <row r="37" spans="1:2" ht="22" customHeight="1">
       <c r="A37" s="3" t="s">
-        <v>1860</v>
+        <v>1869</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>1861</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="38" spans="1:2" ht="22" customHeight="1">
       <c r="A38" s="3" t="s">
-        <v>1862</v>
+        <v>1871</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>1863</v>
+        <v>1872</v>
       </c>
     </row>
     <row r="39" spans="1:2" ht="22" customHeight="1">
       <c r="A39" s="3" t="s">
-        <v>1864</v>
+        <v>1873</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>1865</v>
+        <v>1874</v>
       </c>
     </row>
     <row r="40" spans="1:2" ht="22" customHeight="1">
       <c r="A40" s="3" t="s">
-        <v>1866</v>
+        <v>1875</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>1867</v>
+        <v>1876</v>
       </c>
     </row>
     <row r="41" spans="1:2" ht="22" customHeight="1">
       <c r="A41" s="3" t="s">
-        <v>1868</v>
+        <v>1877</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>1869</v>
+        <v>1878</v>
       </c>
     </row>
     <row r="42" spans="1:2" ht="22" customHeight="1">
@@ -14488,7 +14506,7 @@
         <v>597</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>1870</v>
+        <v>1879</v>
       </c>
     </row>
     <row r="43" spans="1:2" ht="22" customHeight="1">
@@ -14496,7 +14514,7 @@
         <v>596</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>1871</v>
+        <v>1880</v>
       </c>
     </row>
     <row r="44" spans="1:2" ht="22" customHeight="1">
@@ -14504,39 +14522,39 @@
         <v>842</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>1872</v>
+        <v>1881</v>
       </c>
     </row>
     <row r="45" spans="1:2" ht="22" customHeight="1">
       <c r="A45" s="3" t="s">
-        <v>1873</v>
+        <v>1882</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>1874</v>
+        <v>1883</v>
       </c>
     </row>
     <row r="46" spans="1:2" ht="22" customHeight="1">
       <c r="A46" s="3" t="s">
-        <v>1875</v>
+        <v>1884</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>1876</v>
+        <v>1885</v>
       </c>
     </row>
     <row r="47" spans="1:2" ht="22" customHeight="1">
       <c r="A47" s="3" t="s">
-        <v>1877</v>
+        <v>1886</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>1878</v>
+        <v>1887</v>
       </c>
     </row>
     <row r="48" spans="1:2" ht="22" customHeight="1">
       <c r="A48" s="3" t="s">
-        <v>1879</v>
+        <v>1888</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>1880</v>
+        <v>1889</v>
       </c>
     </row>
   </sheetData>
@@ -14575,278 +14593,278 @@
     </row>
     <row r="3" spans="1:3" ht="22" customHeight="1">
       <c r="A3" s="5" t="s">
-        <v>1881</v>
+        <v>1890</v>
       </c>
       <c r="B3" s="5"/>
       <c r="C3" s="5"/>
     </row>
     <row r="4" spans="1:3" ht="32" customHeight="1">
       <c r="A4" s="6" t="s">
-        <v>962</v>
+        <v>966</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>1882</v>
+        <v>1891</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>1883</v>
+        <v>1892</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="18" customHeight="1">
       <c r="A5" s="9" t="s">
-        <v>1884</v>
+        <v>1893</v>
       </c>
       <c r="B5" s="9"/>
       <c r="C5" s="9"/>
     </row>
     <row r="6" spans="1:3" ht="26" customHeight="1">
       <c r="A6" s="4" t="s">
-        <v>1884</v>
+        <v>1893</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>1885</v>
+        <v>1894</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>1886</v>
+        <v>1895</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="26" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>1884</v>
+        <v>1893</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>1887</v>
+        <v>1896</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>1888</v>
+        <v>1897</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="26" customHeight="1">
       <c r="A8" s="4" t="s">
-        <v>1884</v>
+        <v>1893</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>1889</v>
+        <v>1898</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>1890</v>
+        <v>1899</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="26" customHeight="1">
       <c r="A9" s="4" t="s">
-        <v>1884</v>
+        <v>1893</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>1891</v>
+        <v>1900</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>1892</v>
+        <v>1901</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="26" customHeight="1">
       <c r="A10" s="4" t="s">
-        <v>1884</v>
+        <v>1893</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>1893</v>
+        <v>1902</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>1894</v>
+        <v>1903</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="18" customHeight="1">
       <c r="A11" s="9" t="s">
-        <v>1895</v>
+        <v>1904</v>
       </c>
       <c r="B11" s="9"/>
       <c r="C11" s="9"/>
     </row>
     <row r="12" spans="1:3" ht="26" customHeight="1">
       <c r="A12" s="4" t="s">
-        <v>1895</v>
+        <v>1904</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>1896</v>
+        <v>1905</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>1897</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="26" customHeight="1">
       <c r="A13" s="4" t="s">
-        <v>1895</v>
+        <v>1904</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>1898</v>
+        <v>1907</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>1899</v>
+        <v>1908</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="26" customHeight="1">
       <c r="A14" s="4" t="s">
-        <v>1895</v>
+        <v>1904</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>1900</v>
+        <v>1909</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>1901</v>
+        <v>1910</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="18" customHeight="1">
       <c r="A15" s="9" t="s">
-        <v>1902</v>
+        <v>1911</v>
       </c>
       <c r="B15" s="9"/>
       <c r="C15" s="9"/>
     </row>
     <row r="16" spans="1:3" ht="26" customHeight="1">
       <c r="A16" s="4" t="s">
-        <v>1902</v>
+        <v>1911</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>1903</v>
+        <v>1912</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>1904</v>
+        <v>1913</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="26" customHeight="1">
       <c r="A17" s="4" t="s">
-        <v>1902</v>
+        <v>1911</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>1905</v>
+        <v>1914</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>1906</v>
+        <v>1915</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="26" customHeight="1">
       <c r="A18" s="4" t="s">
-        <v>1902</v>
+        <v>1911</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>1907</v>
+        <v>1916</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>1908</v>
+        <v>1917</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="18" customHeight="1">
       <c r="A19" s="9" t="s">
-        <v>1909</v>
+        <v>1918</v>
       </c>
       <c r="B19" s="9"/>
       <c r="C19" s="9"/>
     </row>
     <row r="20" spans="1:3" ht="26" customHeight="1">
       <c r="A20" s="4" t="s">
-        <v>1909</v>
+        <v>1918</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>1910</v>
+        <v>1919</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>1911</v>
+        <v>1920</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="26" customHeight="1">
       <c r="A21" s="4" t="s">
-        <v>1909</v>
+        <v>1918</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>1912</v>
+        <v>1921</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>1913</v>
+        <v>1922</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="26" customHeight="1">
       <c r="A22" s="4" t="s">
-        <v>1909</v>
+        <v>1918</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>1914</v>
+        <v>1923</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>1915</v>
+        <v>1924</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="18" customHeight="1">
       <c r="A23" s="9" t="s">
-        <v>1916</v>
+        <v>1925</v>
       </c>
       <c r="B23" s="9"/>
       <c r="C23" s="9"/>
     </row>
     <row r="24" spans="1:3" ht="26" customHeight="1">
       <c r="A24" s="4" t="s">
-        <v>1916</v>
+        <v>1925</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>1917</v>
+        <v>1926</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>1918</v>
+        <v>1927</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="26" customHeight="1">
       <c r="A25" s="4" t="s">
-        <v>1916</v>
+        <v>1925</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>1919</v>
+        <v>1928</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>1920</v>
+        <v>1929</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="18" customHeight="1">
       <c r="A26" s="9" t="s">
-        <v>1921</v>
+        <v>1930</v>
       </c>
       <c r="B26" s="9"/>
       <c r="C26" s="9"/>
     </row>
     <row r="27" spans="1:3" ht="26" customHeight="1">
       <c r="A27" s="4" t="s">
-        <v>1921</v>
+        <v>1930</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>1922</v>
+        <v>1931</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>1923</v>
+        <v>1932</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="18" customHeight="1">
       <c r="A28" s="9" t="s">
-        <v>1924</v>
+        <v>1933</v>
       </c>
       <c r="B28" s="9"/>
       <c r="C28" s="9"/>
     </row>
     <row r="29" spans="1:3" ht="26" customHeight="1">
       <c r="A29" s="4" t="s">
-        <v>1924</v>
+        <v>1933</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>1925</v>
+        <v>1934</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>1926</v>
+        <v>1935</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="26" customHeight="1">
       <c r="A30" s="4" t="s">
-        <v>1924</v>
+        <v>1933</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>1927</v>
+        <v>1936</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>1928</v>
+        <v>1937</v>
       </c>
     </row>
   </sheetData>
